--- a/data/BallparkPal_Pitchers.xlsx
+++ b/data/BallparkPal_Pitchers.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="130">
   <si>
     <t>GamePk</t>
   </si>
@@ -89,49 +89,49 @@
     <t>StolenBasesAllowed</t>
   </si>
   <si>
-    <t>2026-04-28</t>
-  </si>
-  <si>
-    <t>7:07</t>
-  </si>
-  <si>
-    <t>Trey Yesavage</t>
-  </si>
-  <si>
-    <t>Yesavage</t>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>3:07</t>
+  </si>
+  <si>
+    <t>Eric Lauer</t>
+  </si>
+  <si>
+    <t>Lauer</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>Brayan Bello</t>
+  </si>
+  <si>
+    <t>Bello</t>
   </si>
   <si>
     <t>R</t>
   </si>
   <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>BOS</t>
-  </si>
-  <si>
-    <t>Payton Tolle</t>
-  </si>
-  <si>
-    <t>Tolle</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
-    <t>8:05</t>
-  </si>
-  <si>
-    <t>Jacob deGrom</t>
-  </si>
-  <si>
-    <t>deGrom</t>
+    <t>2:35</t>
+  </si>
+  <si>
+    <t>Nathan Eovaldi</t>
+  </si>
+  <si>
+    <t>Eovaldi</t>
   </si>
   <si>
     <t>TEX</t>
@@ -140,268 +140,271 @@
     <t>NYY</t>
   </si>
   <si>
-    <t>Cam Schlittler</t>
-  </si>
-  <si>
-    <t>Schlittler</t>
+    <t>Elmer Rodriguez</t>
+  </si>
+  <si>
+    <t>Rodriguez</t>
+  </si>
+  <si>
+    <t>4:10</t>
+  </si>
+  <si>
+    <t>Jameson Taillon</t>
+  </si>
+  <si>
+    <t>Taillon</t>
+  </si>
+  <si>
+    <t>CHC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD </t>
+  </si>
+  <si>
+    <t>Matt Waldron</t>
+  </si>
+  <si>
+    <t>Waldron</t>
+  </si>
+  <si>
+    <t>6:40</t>
+  </si>
+  <si>
+    <t>Andre Pallante</t>
+  </si>
+  <si>
+    <t>Pallante</t>
+  </si>
+  <si>
+    <t>STL</t>
+  </si>
+  <si>
+    <t>PIT</t>
+  </si>
+  <si>
+    <t>Bubba Chandler</t>
+  </si>
+  <si>
+    <t>Chandler</t>
+  </si>
+  <si>
+    <t>Cristopher Sanchez</t>
+  </si>
+  <si>
+    <t>Sanchez</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF </t>
+  </si>
+  <si>
+    <t>Logan Webb</t>
+  </si>
+  <si>
+    <t>Webb</t>
+  </si>
+  <si>
+    <t>7:10</t>
+  </si>
+  <si>
+    <t>David Peterson</t>
+  </si>
+  <si>
+    <t>Peterson</t>
+  </si>
+  <si>
+    <t>NYM</t>
+  </si>
+  <si>
+    <t>WAS</t>
+  </si>
+  <si>
+    <t>Cade Cavalli</t>
+  </si>
+  <si>
+    <t>Cavalli</t>
+  </si>
+  <si>
+    <t>1:40</t>
+  </si>
+  <si>
+    <t>George Kirby</t>
+  </si>
+  <si>
+    <t>Kirby</t>
+  </si>
+  <si>
+    <t>SEA</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>Taj Bradley</t>
+  </si>
+  <si>
+    <t>Bradley</t>
+  </si>
+  <si>
+    <t>7:40</t>
+  </si>
+  <si>
+    <t>Eduardo Rodriguez</t>
+  </si>
+  <si>
+    <t>ARI</t>
+  </si>
+  <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>Brandon Sproat</t>
+  </si>
+  <si>
+    <t>Sproat</t>
+  </si>
+  <si>
+    <t>3:10</t>
+  </si>
+  <si>
+    <t>Tyler Glasnow</t>
+  </si>
+  <si>
+    <t>Glasnow</t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>Sandy Alcantara</t>
+  </si>
+  <si>
+    <t>Alcantara</t>
+  </si>
+  <si>
+    <t>1:10</t>
+  </si>
+  <si>
+    <t>Drew Rasmussen</t>
+  </si>
+  <si>
+    <t>Rasmussen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB </t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t>Gavin Williams</t>
+  </si>
+  <si>
+    <t>Williams</t>
+  </si>
+  <si>
+    <t>Tomoyuki Sugano</t>
+  </si>
+  <si>
+    <t>Sugano</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t>CIN</t>
+  </si>
+  <si>
+    <t>Brandon Williamson</t>
+  </si>
+  <si>
+    <t>Williamson</t>
+  </si>
+  <si>
+    <t>Yusei Kikuchi</t>
+  </si>
+  <si>
+    <t>Kikuchi</t>
+  </si>
+  <si>
+    <t>LAA</t>
+  </si>
+  <si>
+    <t>CHW</t>
+  </si>
+  <si>
+    <t>Erick Fedde</t>
+  </si>
+  <si>
+    <t>Fedde</t>
+  </si>
+  <si>
+    <t>6:35</t>
+  </si>
+  <si>
+    <t>Chris Bassitt</t>
+  </si>
+  <si>
+    <t>Bassitt</t>
+  </si>
+  <si>
+    <t>BAL</t>
+  </si>
+  <si>
+    <t>HOU</t>
+  </si>
+  <si>
+    <t>Peter Lambert</t>
+  </si>
+  <si>
+    <t>Lambert</t>
+  </si>
+  <si>
+    <t>7:15</t>
+  </si>
+  <si>
+    <t>Tarik Skubal</t>
+  </si>
+  <si>
+    <t>Skubal</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>JR Ritchie</t>
+  </si>
+  <si>
+    <t>Ritchie</t>
   </si>
   <si>
     <t>9:40</t>
   </si>
   <si>
-    <t>Walker Buehler</t>
-  </si>
-  <si>
-    <t>Buehler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SD </t>
-  </si>
-  <si>
-    <t>CHC</t>
-  </si>
-  <si>
-    <t>Edward Cabrera</t>
-  </si>
-  <si>
-    <t>Cabrera</t>
-  </si>
-  <si>
-    <t>6:40</t>
-  </si>
-  <si>
-    <t>Braxton Ashcraft</t>
-  </si>
-  <si>
-    <t>Ashcraft</t>
-  </si>
-  <si>
-    <t>PIT</t>
-  </si>
-  <si>
-    <t>STL</t>
-  </si>
-  <si>
-    <t>Kyle Leahy</t>
-  </si>
-  <si>
-    <t>Leahy</t>
-  </si>
-  <si>
-    <t>Tyler Mahle</t>
-  </si>
-  <si>
-    <t>Mahle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF </t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>Jesus Luzardo</t>
-  </si>
-  <si>
-    <t>Luzardo</t>
-  </si>
-  <si>
-    <t>7:10</t>
-  </si>
-  <si>
-    <t>Clay Holmes</t>
-  </si>
-  <si>
-    <t>Holmes</t>
-  </si>
-  <si>
-    <t>NYM</t>
-  </si>
-  <si>
-    <t>WAS</t>
-  </si>
-  <si>
-    <t>Zack Littell</t>
-  </si>
-  <si>
-    <t>Littell</t>
-  </si>
-  <si>
-    <t>7:40</t>
-  </si>
-  <si>
-    <t>Joe Ryan</t>
-  </si>
-  <si>
-    <t>Ryan</t>
-  </si>
-  <si>
-    <t>MIN</t>
-  </si>
-  <si>
-    <t>SEA</t>
-  </si>
-  <si>
-    <t>Logan Gilbert</t>
-  </si>
-  <si>
-    <t>Gilbert</t>
-  </si>
-  <si>
-    <t>Merrill Kelly</t>
-  </si>
-  <si>
-    <t>Kelly</t>
-  </si>
-  <si>
-    <t>ARI</t>
-  </si>
-  <si>
-    <t>MIL</t>
-  </si>
-  <si>
-    <t>Chad Patrick</t>
-  </si>
-  <si>
-    <t>Patrick</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>Shohei Ohtani</t>
-  </si>
-  <si>
-    <t>Ohtani</t>
-  </si>
-  <si>
-    <t>LAD</t>
-  </si>
-  <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>Janson Junk</t>
-  </si>
-  <si>
-    <t>Junk</t>
-  </si>
-  <si>
-    <t>6:10</t>
-  </si>
-  <si>
-    <t>Nick Martinez</t>
-  </si>
-  <si>
-    <t>Martinez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB </t>
-  </si>
-  <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>Tanner Bibee</t>
-  </si>
-  <si>
-    <t>Bibee</t>
-  </si>
-  <si>
-    <t>Kyle Freeland</t>
-  </si>
-  <si>
-    <t>Freeland</t>
-  </si>
-  <si>
-    <t>COL</t>
-  </si>
-  <si>
-    <t>CIN</t>
-  </si>
-  <si>
-    <t>Chase Burns</t>
-  </si>
-  <si>
-    <t>Burns</t>
-  </si>
-  <si>
-    <t>Davis Martin</t>
-  </si>
-  <si>
-    <t>Martin</t>
-  </si>
-  <si>
-    <t>CHW</t>
-  </si>
-  <si>
-    <t>LAA</t>
-  </si>
-  <si>
-    <t>Jose Soriano</t>
-  </si>
-  <si>
-    <t>Soriano</t>
-  </si>
-  <si>
-    <t>6:35</t>
-  </si>
-  <si>
-    <t>Shane Baz</t>
-  </si>
-  <si>
-    <t>Baz</t>
-  </si>
-  <si>
-    <t>BAL</t>
-  </si>
-  <si>
-    <t>HOU</t>
-  </si>
-  <si>
-    <t>Kai-Wei Teng</t>
-  </si>
-  <si>
-    <t>Teng</t>
-  </si>
-  <si>
-    <t>7:15</t>
-  </si>
-  <si>
-    <t>Martin Perez</t>
-  </si>
-  <si>
-    <t>Perez</t>
-  </si>
-  <si>
-    <t>ATL</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>Casey Mize</t>
-  </si>
-  <si>
-    <t>Mize</t>
-  </si>
-  <si>
-    <t>Aaron Civale</t>
-  </si>
-  <si>
-    <t>Civale</t>
+    <t>Michael Wacha</t>
+  </si>
+  <si>
+    <t>Wacha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KC </t>
   </si>
   <si>
     <t>ATH</t>
   </si>
   <si>
-    <t xml:space="preserve">KC </t>
-  </si>
-  <si>
-    <t>Kris Bubic</t>
-  </si>
-  <si>
-    <t>Bubic</t>
+    <t>Luis Severino</t>
+  </si>
+  <si>
+    <t>Severino</t>
   </si>
 </sst>
 </file>
@@ -820,7 +823,7 @@
     </row>
     <row r="2" spans="1:24">
       <c r="A2">
-        <v>822823</v>
+        <v>822821</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
@@ -829,7 +832,7 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>702056</v>
+        <v>641778</v>
       </c>
       <c r="E2" t="s">
         <v>26</v>
@@ -850,51 +853,51 @@
         <v>31</v>
       </c>
       <c r="K2">
-        <v>21.067</v>
+        <v>19.981</v>
       </c>
       <c r="L2">
-        <v>5.204</v>
+        <v>4.68</v>
       </c>
       <c r="M2">
-        <v>0.302</v>
+        <v>0.243</v>
       </c>
       <c r="N2">
-        <v>0.248</v>
+        <v>0.271</v>
       </c>
       <c r="O2">
-        <v>0.45</v>
+        <v>0.486</v>
       </c>
       <c r="P2">
-        <v>0.306</v>
+        <v>0.143</v>
       </c>
       <c r="Q2">
-        <v>21.044</v>
+        <v>10.778</v>
       </c>
       <c r="R2">
-        <v>35.812</v>
+        <v>20.436</v>
       </c>
       <c r="S2">
-        <v>1.658</v>
+        <v>2.299</v>
       </c>
       <c r="T2">
-        <v>3.76</v>
+        <v>4.575</v>
       </c>
       <c r="U2">
-        <v>7.379</v>
+        <v>3.753</v>
       </c>
       <c r="V2">
-        <v>1.795</v>
+        <v>1.482</v>
       </c>
       <c r="W2">
-        <v>0.571</v>
+        <v>0.768</v>
       </c>
       <c r="X2">
-        <v>0.357</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="3" spans="1:24">
       <c r="A3">
-        <v>822823</v>
+        <v>822821</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
@@ -903,7 +906,7 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>801139</v>
+        <v>678394</v>
       </c>
       <c r="E3" t="s">
         <v>32</v>
@@ -924,51 +927,51 @@
         <v>30</v>
       </c>
       <c r="K3">
-        <v>19.027</v>
+        <v>21.685</v>
       </c>
       <c r="L3">
-        <v>4.417</v>
+        <v>4.889</v>
       </c>
       <c r="M3">
-        <v>0.104</v>
+        <v>0.162</v>
       </c>
       <c r="N3">
-        <v>0.34</v>
+        <v>0.381</v>
       </c>
       <c r="O3">
-        <v>0.556</v>
+        <v>0.457</v>
       </c>
       <c r="P3">
-        <v>0.088</v>
+        <v>0.223</v>
       </c>
       <c r="Q3">
-        <v>12.724</v>
+        <v>6.408</v>
       </c>
       <c r="R3">
-        <v>23.1</v>
+        <v>15.291</v>
       </c>
       <c r="S3">
-        <v>1.92</v>
+        <v>3.002</v>
       </c>
       <c r="T3">
-        <v>4.045</v>
+        <v>5.491</v>
       </c>
       <c r="U3">
-        <v>4.877</v>
+        <v>2.587</v>
       </c>
       <c r="V3">
-        <v>1.865</v>
+        <v>1.877</v>
       </c>
       <c r="W3">
-        <v>0.533</v>
+        <v>0.954</v>
       </c>
       <c r="X3">
-        <v>0.364</v>
+        <v>0.381</v>
       </c>
     </row>
     <row r="4" spans="1:24">
       <c r="A4">
-        <v>822908</v>
+        <v>822907</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -977,7 +980,7 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>594798</v>
+        <v>543135</v>
       </c>
       <c r="E4" t="s">
         <v>37</v>
@@ -986,7 +989,7 @@
         <v>38</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s">
         <v>29</v>
@@ -998,51 +1001,51 @@
         <v>40</v>
       </c>
       <c r="K4">
-        <v>23.284</v>
+        <v>25.067</v>
       </c>
       <c r="L4">
-        <v>5.822</v>
+        <v>6.083</v>
       </c>
       <c r="M4">
-        <v>0.237</v>
+        <v>0.377</v>
       </c>
       <c r="N4">
-        <v>0.36</v>
+        <v>0.277</v>
       </c>
       <c r="O4">
-        <v>0.403</v>
+        <v>0.346</v>
       </c>
       <c r="P4">
-        <v>0.475</v>
+        <v>0.511</v>
       </c>
       <c r="Q4">
-        <v>21.336</v>
+        <v>17.934</v>
       </c>
       <c r="R4">
-        <v>37.036</v>
+        <v>32.951</v>
       </c>
       <c r="S4">
-        <v>2.071</v>
+        <v>2.601</v>
       </c>
       <c r="T4">
-        <v>4.075</v>
+        <v>5.273</v>
       </c>
       <c r="U4">
-        <v>7.486</v>
+        <v>6.066</v>
       </c>
       <c r="V4">
-        <v>1.888</v>
+        <v>1.827</v>
       </c>
       <c r="W4">
-        <v>0.845</v>
+        <v>0.899</v>
       </c>
       <c r="X4">
-        <v>0.813</v>
+        <v>0.445</v>
       </c>
     </row>
     <row r="5" spans="1:24">
       <c r="A5">
-        <v>822908</v>
+        <v>822907</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1051,7 +1054,7 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>693645</v>
+        <v>695684</v>
       </c>
       <c r="E5" t="s">
         <v>41</v>
@@ -1060,7 +1063,7 @@
         <v>42</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
         <v>35</v>
@@ -1072,51 +1075,51 @@
         <v>39</v>
       </c>
       <c r="K5">
-        <v>23.377</v>
+        <v>18.944</v>
       </c>
       <c r="L5">
-        <v>5.893</v>
+        <v>4.244</v>
       </c>
       <c r="M5">
-        <v>0.264</v>
+        <v>0.094</v>
       </c>
       <c r="N5">
-        <v>0.247</v>
+        <v>0.345</v>
       </c>
       <c r="O5">
-        <v>0.489</v>
+        <v>0.561</v>
       </c>
       <c r="P5">
-        <v>0.569</v>
+        <v>0.064</v>
       </c>
       <c r="Q5">
-        <v>20.559</v>
+        <v>8.335</v>
       </c>
       <c r="R5">
-        <v>36.162</v>
+        <v>17.008</v>
       </c>
       <c r="S5">
-        <v>1.764</v>
+        <v>2.476</v>
       </c>
       <c r="T5">
-        <v>4.44</v>
+        <v>4.668</v>
       </c>
       <c r="U5">
-        <v>6.637</v>
+        <v>3.628</v>
       </c>
       <c r="V5">
-        <v>1.457</v>
+        <v>1.824</v>
       </c>
       <c r="W5">
-        <v>0.479</v>
+        <v>0.612</v>
       </c>
       <c r="X5">
-        <v>0.348</v>
+        <v>0.339</v>
       </c>
     </row>
     <row r="6" spans="1:24">
       <c r="A6">
-        <v>823310</v>
+        <v>823312</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -1125,7 +1128,7 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>621111</v>
+        <v>592791</v>
       </c>
       <c r="E6" t="s">
         <v>44</v>
@@ -1134,10 +1137,10 @@
         <v>45</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I6" t="s">
         <v>46</v>
@@ -1146,51 +1149,51 @@
         <v>47</v>
       </c>
       <c r="K6">
-        <v>22.182</v>
+        <v>22.162</v>
       </c>
       <c r="L6">
-        <v>5.095</v>
+        <v>5.256</v>
       </c>
       <c r="M6">
-        <v>0.259</v>
+        <v>0.223</v>
       </c>
       <c r="N6">
-        <v>0.3</v>
+        <v>0.261</v>
       </c>
       <c r="O6">
-        <v>0.441</v>
+        <v>0.516</v>
       </c>
       <c r="P6">
-        <v>0.278</v>
+        <v>0.319</v>
       </c>
       <c r="Q6">
-        <v>11.795</v>
+        <v>12.617</v>
       </c>
       <c r="R6">
-        <v>23.27</v>
+        <v>24.064</v>
       </c>
       <c r="S6">
-        <v>2.346</v>
+        <v>2.49</v>
       </c>
       <c r="T6">
-        <v>4.552</v>
+        <v>4.641</v>
       </c>
       <c r="U6">
-        <v>4.119</v>
+        <v>4.385</v>
       </c>
       <c r="V6">
-        <v>2.544</v>
+        <v>1.867</v>
       </c>
       <c r="W6">
-        <v>0.549</v>
+        <v>0.828</v>
       </c>
       <c r="X6">
-        <v>0.498</v>
+        <v>0.438</v>
       </c>
     </row>
     <row r="7" spans="1:24">
       <c r="A7">
-        <v>823310</v>
+        <v>823312</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -1199,7 +1202,7 @@
         <v>43</v>
       </c>
       <c r="D7">
-        <v>665795</v>
+        <v>663362</v>
       </c>
       <c r="E7" t="s">
         <v>48</v>
@@ -1208,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I7" t="s">
         <v>47</v>
@@ -1220,51 +1223,51 @@
         <v>46</v>
       </c>
       <c r="K7">
-        <v>22.462</v>
+        <v>23.261</v>
       </c>
       <c r="L7">
-        <v>5.176</v>
+        <v>5.087</v>
       </c>
       <c r="M7">
-        <v>0.196</v>
+        <v>0.226</v>
       </c>
       <c r="N7">
-        <v>0.329</v>
+        <v>0.384</v>
       </c>
       <c r="O7">
-        <v>0.475</v>
+        <v>0.39</v>
       </c>
       <c r="P7">
-        <v>0.322</v>
+        <v>0.274</v>
       </c>
       <c r="Q7">
-        <v>12.309</v>
+        <v>9.75</v>
       </c>
       <c r="R7">
-        <v>24.255</v>
+        <v>21.217</v>
       </c>
       <c r="S7">
-        <v>2.448</v>
+        <v>2.999</v>
       </c>
       <c r="T7">
-        <v>4.682</v>
+        <v>5.1</v>
       </c>
       <c r="U7">
-        <v>4.537</v>
+        <v>4.166</v>
       </c>
       <c r="V7">
-        <v>2.489</v>
+        <v>3.14</v>
       </c>
       <c r="W7">
-        <v>0.565</v>
+        <v>0.758</v>
       </c>
       <c r="X7">
-        <v>0.504</v>
+        <v>0.573</v>
       </c>
     </row>
     <row r="8" spans="1:24">
       <c r="A8">
-        <v>823390</v>
+        <v>823392</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
@@ -1273,7 +1276,7 @@
         <v>50</v>
       </c>
       <c r="D8">
-        <v>677952</v>
+        <v>669467</v>
       </c>
       <c r="E8" t="s">
         <v>51</v>
@@ -1282,10 +1285,10 @@
         <v>52</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H8" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I8" t="s">
         <v>53</v>
@@ -1294,51 +1297,51 @@
         <v>54</v>
       </c>
       <c r="K8">
-        <v>24.004</v>
+        <v>22.341</v>
       </c>
       <c r="L8">
-        <v>5.9</v>
+        <v>5.047</v>
       </c>
       <c r="M8">
-        <v>0.4</v>
+        <v>0.148</v>
       </c>
       <c r="N8">
-        <v>0.196</v>
+        <v>0.409</v>
       </c>
       <c r="O8">
-        <v>0.404</v>
+        <v>0.443</v>
       </c>
       <c r="P8">
-        <v>0.528</v>
+        <v>0.26</v>
       </c>
       <c r="Q8">
-        <v>19.264</v>
+        <v>8.918</v>
       </c>
       <c r="R8">
-        <v>34.603</v>
+        <v>19.32</v>
       </c>
       <c r="S8">
-        <v>1.833</v>
+        <v>2.654</v>
       </c>
       <c r="T8">
-        <v>4.105</v>
+        <v>5.032</v>
       </c>
       <c r="U8">
-        <v>5.963</v>
+        <v>3.406</v>
       </c>
       <c r="V8">
-        <v>2.414</v>
+        <v>2.526</v>
       </c>
       <c r="W8">
-        <v>0.457</v>
+        <v>0.501</v>
       </c>
       <c r="X8">
-        <v>0.454</v>
+        <v>0.508</v>
       </c>
     </row>
     <row r="9" spans="1:24">
       <c r="A9">
-        <v>823390</v>
+        <v>823392</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
@@ -1347,7 +1350,7 @@
         <v>50</v>
       </c>
       <c r="D9">
-        <v>681517</v>
+        <v>696149</v>
       </c>
       <c r="E9" t="s">
         <v>55</v>
@@ -1356,10 +1359,10 @@
         <v>56</v>
       </c>
       <c r="G9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I9" t="s">
         <v>54</v>
@@ -1368,51 +1371,51 @@
         <v>53</v>
       </c>
       <c r="K9">
-        <v>19.03</v>
+        <v>23.008</v>
       </c>
       <c r="L9">
-        <v>4.315</v>
+        <v>5.567</v>
       </c>
       <c r="M9">
-        <v>0.08</v>
+        <v>0.365</v>
       </c>
       <c r="N9">
-        <v>0.385</v>
+        <v>0.22</v>
       </c>
       <c r="O9">
-        <v>0.535</v>
+        <v>0.415</v>
       </c>
       <c r="P9">
-        <v>0.074</v>
+        <v>0.431</v>
       </c>
       <c r="Q9">
-        <v>8.144</v>
+        <v>16.239</v>
       </c>
       <c r="R9">
-        <v>16.599</v>
+        <v>29.794</v>
       </c>
       <c r="S9">
-        <v>2.185</v>
+        <v>1.952</v>
       </c>
       <c r="T9">
-        <v>4.437</v>
+        <v>4.171</v>
       </c>
       <c r="U9">
-        <v>3.146</v>
+        <v>5.011</v>
       </c>
       <c r="V9">
-        <v>1.903</v>
+        <v>2.306</v>
       </c>
       <c r="W9">
-        <v>0.442</v>
+        <v>0.537</v>
       </c>
       <c r="X9">
-        <v>0.345</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="10" spans="1:24">
       <c r="A10">
-        <v>823473</v>
+        <v>823471</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -1421,7 +1424,7 @@
         <v>50</v>
       </c>
       <c r="D10">
-        <v>641816</v>
+        <v>650911</v>
       </c>
       <c r="E10" t="s">
         <v>57</v>
@@ -1433,7 +1436,7 @@
         <v>28</v>
       </c>
       <c r="H10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I10" t="s">
         <v>59</v>
@@ -1442,51 +1445,51 @@
         <v>60</v>
       </c>
       <c r="K10">
-        <v>21.835</v>
+        <v>24.559</v>
       </c>
       <c r="L10">
-        <v>4.921</v>
+        <v>5.987</v>
       </c>
       <c r="M10">
-        <v>0.136</v>
+        <v>0.377</v>
       </c>
       <c r="N10">
-        <v>0.418</v>
+        <v>0.252</v>
       </c>
       <c r="O10">
-        <v>0.446</v>
+        <v>0.371</v>
       </c>
       <c r="P10">
-        <v>0.229</v>
+        <v>0.562</v>
       </c>
       <c r="Q10">
-        <v>10.29</v>
+        <v>19.441</v>
       </c>
       <c r="R10">
-        <v>21.053</v>
+        <v>35.362</v>
       </c>
       <c r="S10">
-        <v>2.785</v>
+        <v>2.058</v>
       </c>
       <c r="T10">
-        <v>5.292</v>
+        <v>5.488</v>
       </c>
       <c r="U10">
-        <v>4.304</v>
+        <v>6.354</v>
       </c>
       <c r="V10">
-        <v>1.986</v>
+        <v>1.472</v>
       </c>
       <c r="W10">
-        <v>0.815</v>
+        <v>0.522</v>
       </c>
       <c r="X10">
-        <v>0.468</v>
+        <v>0.244</v>
       </c>
     </row>
     <row r="11" spans="1:24">
       <c r="A11">
-        <v>823473</v>
+        <v>823471</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
@@ -1495,7 +1498,7 @@
         <v>50</v>
       </c>
       <c r="D11">
-        <v>666200</v>
+        <v>657277</v>
       </c>
       <c r="E11" t="s">
         <v>61</v>
@@ -1507,7 +1510,7 @@
         <v>34</v>
       </c>
       <c r="H11" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I11" t="s">
         <v>60</v>
@@ -1516,51 +1519,51 @@
         <v>59</v>
       </c>
       <c r="K11">
-        <v>24.475</v>
+        <v>23.859</v>
       </c>
       <c r="L11">
-        <v>5.875</v>
+        <v>5.597</v>
       </c>
       <c r="M11">
-        <v>0.4</v>
+        <v>0.188</v>
       </c>
       <c r="N11">
-        <v>0.222</v>
+        <v>0.397</v>
       </c>
       <c r="O11">
-        <v>0.379</v>
+        <v>0.415</v>
       </c>
       <c r="P11">
-        <v>0.498</v>
+        <v>0.438</v>
       </c>
       <c r="Q11">
-        <v>19.709</v>
+        <v>13.428</v>
       </c>
       <c r="R11">
-        <v>35.627</v>
+        <v>26.481</v>
       </c>
       <c r="S11">
-        <v>2.226</v>
+        <v>2.648</v>
       </c>
       <c r="T11">
-        <v>5.434</v>
+        <v>5.559</v>
       </c>
       <c r="U11">
-        <v>6.763</v>
+        <v>4.918</v>
       </c>
       <c r="V11">
-        <v>1.619</v>
+        <v>1.884</v>
       </c>
       <c r="W11">
-        <v>0.598</v>
+        <v>0.603</v>
       </c>
       <c r="X11">
-        <v>0.25</v>
+        <v>0.643</v>
       </c>
     </row>
     <row r="12" spans="1:24">
       <c r="A12">
-        <v>823636</v>
+        <v>823633</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
@@ -1569,7 +1572,7 @@
         <v>63</v>
       </c>
       <c r="D12">
-        <v>605280</v>
+        <v>656849</v>
       </c>
       <c r="E12" t="s">
         <v>64</v>
@@ -1590,51 +1593,51 @@
         <v>67</v>
       </c>
       <c r="K12">
-        <v>22.485</v>
+        <v>21.448</v>
       </c>
       <c r="L12">
-        <v>5.389</v>
+        <v>4.832</v>
       </c>
       <c r="M12">
-        <v>0.319</v>
+        <v>0.224</v>
       </c>
       <c r="N12">
-        <v>0.239</v>
+        <v>0.321</v>
       </c>
       <c r="O12">
-        <v>0.442</v>
+        <v>0.455</v>
       </c>
       <c r="P12">
-        <v>0.382</v>
+        <v>0.233</v>
       </c>
       <c r="Q12">
-        <v>12.137</v>
+        <v>11.386</v>
       </c>
       <c r="R12">
-        <v>23.782</v>
+        <v>22.8</v>
       </c>
       <c r="S12">
-        <v>1.982</v>
+        <v>2.402</v>
       </c>
       <c r="T12">
-        <v>4.529</v>
+        <v>5.137</v>
       </c>
       <c r="U12">
-        <v>3.373</v>
+        <v>4.411</v>
       </c>
       <c r="V12">
-        <v>2.238</v>
+        <v>2.197</v>
       </c>
       <c r="W12">
-        <v>0.418</v>
+        <v>0.439</v>
       </c>
       <c r="X12">
-        <v>0.852</v>
+        <v>0.749</v>
       </c>
     </row>
     <row r="13" spans="1:24">
       <c r="A13">
-        <v>823636</v>
+        <v>823633</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -1643,7 +1646,7 @@
         <v>63</v>
       </c>
       <c r="D13">
-        <v>641793</v>
+        <v>676917</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
@@ -1652,7 +1655,7 @@
         <v>69</v>
       </c>
       <c r="G13" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H13" t="s">
         <v>35</v>
@@ -1664,51 +1667,51 @@
         <v>66</v>
       </c>
       <c r="K13">
-        <v>21.845</v>
+        <v>20.94</v>
       </c>
       <c r="L13">
-        <v>5.135</v>
+        <v>4.868</v>
       </c>
       <c r="M13">
-        <v>0.164</v>
+        <v>0.168</v>
       </c>
       <c r="N13">
-        <v>0.375</v>
+        <v>0.288</v>
       </c>
       <c r="O13">
-        <v>0.461</v>
+        <v>0.544</v>
       </c>
       <c r="P13">
-        <v>0.281</v>
+        <v>0.209</v>
       </c>
       <c r="Q13">
-        <v>10.182</v>
+        <v>11.95</v>
       </c>
       <c r="R13">
-        <v>20.397</v>
+        <v>22.909</v>
       </c>
       <c r="S13">
-        <v>2.493</v>
+        <v>2.136</v>
       </c>
       <c r="T13">
-        <v>5.046</v>
+        <v>4.453</v>
       </c>
       <c r="U13">
-        <v>3.455</v>
+        <v>4.289</v>
       </c>
       <c r="V13">
-        <v>1.538</v>
+        <v>2.185</v>
       </c>
       <c r="W13">
-        <v>0.869</v>
+        <v>0.554</v>
       </c>
       <c r="X13">
-        <v>0.495</v>
+        <v>0.511</v>
       </c>
     </row>
     <row r="14" spans="1:24">
       <c r="A14">
-        <v>823716</v>
+        <v>823717</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
@@ -1717,7 +1720,7 @@
         <v>70</v>
       </c>
       <c r="D14">
-        <v>657746</v>
+        <v>669923</v>
       </c>
       <c r="E14" t="s">
         <v>71</v>
@@ -1726,10 +1729,10 @@
         <v>72</v>
       </c>
       <c r="G14" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H14" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I14" t="s">
         <v>73</v>
@@ -1738,51 +1741,51 @@
         <v>74</v>
       </c>
       <c r="K14">
-        <v>23.034</v>
+        <v>23.173</v>
       </c>
       <c r="L14">
-        <v>5.576</v>
+        <v>5.492</v>
       </c>
       <c r="M14">
-        <v>0.284</v>
+        <v>0.231</v>
       </c>
       <c r="N14">
-        <v>0.31</v>
+        <v>0.286</v>
       </c>
       <c r="O14">
-        <v>0.406</v>
+        <v>0.483</v>
       </c>
       <c r="P14">
-        <v>0.418</v>
+        <v>0.415</v>
       </c>
       <c r="Q14">
-        <v>17.051</v>
+        <v>13.405</v>
       </c>
       <c r="R14">
-        <v>30.83</v>
+        <v>25.92</v>
       </c>
       <c r="S14">
-        <v>2.25</v>
+        <v>2.318</v>
       </c>
       <c r="T14">
-        <v>4.541</v>
+        <v>5.074</v>
       </c>
       <c r="U14">
-        <v>5.825</v>
+        <v>4.45</v>
       </c>
       <c r="V14">
-        <v>1.785</v>
+        <v>1.845</v>
       </c>
       <c r="W14">
-        <v>0.808</v>
+        <v>0.635</v>
       </c>
       <c r="X14">
-        <v>0.446</v>
+        <v>0.481</v>
       </c>
     </row>
     <row r="15" spans="1:24">
       <c r="A15">
-        <v>823716</v>
+        <v>823717</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
@@ -1791,7 +1794,7 @@
         <v>70</v>
       </c>
       <c r="D15">
-        <v>669302</v>
+        <v>671737</v>
       </c>
       <c r="E15" t="s">
         <v>75</v>
@@ -1800,10 +1803,10 @@
         <v>76</v>
       </c>
       <c r="G15" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H15" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I15" t="s">
         <v>74</v>
@@ -1812,66 +1815,66 @@
         <v>73</v>
       </c>
       <c r="K15">
-        <v>22.398</v>
+        <v>24.022</v>
       </c>
       <c r="L15">
-        <v>5.3</v>
+        <v>5.565</v>
       </c>
       <c r="M15">
-        <v>0.208</v>
+        <v>0.266</v>
       </c>
       <c r="N15">
-        <v>0.305</v>
+        <v>0.342</v>
       </c>
       <c r="O15">
-        <v>0.486</v>
+        <v>0.392</v>
       </c>
       <c r="P15">
-        <v>0.352</v>
+        <v>0.427</v>
       </c>
       <c r="Q15">
-        <v>15.463</v>
+        <v>16.546</v>
       </c>
       <c r="R15">
-        <v>28.56</v>
+        <v>31.09</v>
       </c>
       <c r="S15">
-        <v>2.33</v>
+        <v>2.438</v>
       </c>
       <c r="T15">
-        <v>5.063</v>
+        <v>4.571</v>
       </c>
       <c r="U15">
-        <v>5.664</v>
+        <v>6.134</v>
       </c>
       <c r="V15">
-        <v>1.561</v>
+        <v>2.84</v>
       </c>
       <c r="W15">
-        <v>0.618</v>
+        <v>0.672</v>
       </c>
       <c r="X15">
-        <v>0.408</v>
+        <v>0.304</v>
       </c>
     </row>
     <row r="16" spans="1:24">
       <c r="A16">
-        <v>823798</v>
+        <v>823796</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D16">
-        <v>518876</v>
+        <v>593958</v>
       </c>
       <c r="E16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="G16" t="s">
         <v>28</v>
@@ -1886,60 +1889,60 @@
         <v>80</v>
       </c>
       <c r="K16">
-        <v>22.533</v>
+        <v>22.61</v>
       </c>
       <c r="L16">
-        <v>5.134</v>
+        <v>5.094</v>
       </c>
       <c r="M16">
-        <v>0.16</v>
+        <v>0.175</v>
       </c>
       <c r="N16">
-        <v>0.399</v>
+        <v>0.37</v>
       </c>
       <c r="O16">
-        <v>0.441</v>
+        <v>0.455</v>
       </c>
       <c r="P16">
-        <v>0.279</v>
+        <v>0.299</v>
       </c>
       <c r="Q16">
-        <v>10.572</v>
+        <v>8.705</v>
       </c>
       <c r="R16">
-        <v>21.692</v>
+        <v>19.246</v>
       </c>
       <c r="S16">
-        <v>2.932</v>
+        <v>2.83</v>
       </c>
       <c r="T16">
-        <v>5.443</v>
+        <v>5.283</v>
       </c>
       <c r="U16">
-        <v>4.337</v>
+        <v>3.402</v>
       </c>
       <c r="V16">
-        <v>1.95</v>
+        <v>2.391</v>
       </c>
       <c r="W16">
-        <v>0.911</v>
+        <v>0.644</v>
       </c>
       <c r="X16">
-        <v>1.047</v>
+        <v>0.651</v>
       </c>
     </row>
     <row r="17" spans="1:24">
       <c r="A17">
-        <v>823798</v>
+        <v>823796</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D17">
-        <v>694477</v>
+        <v>687075</v>
       </c>
       <c r="E17" t="s">
         <v>81</v>
@@ -1948,7 +1951,7 @@
         <v>82</v>
       </c>
       <c r="G17" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H17" t="s">
         <v>29</v>
@@ -1960,51 +1963,51 @@
         <v>79</v>
       </c>
       <c r="K17">
-        <v>20.039</v>
+        <v>22.172</v>
       </c>
       <c r="L17">
-        <v>4.8</v>
+        <v>5.055</v>
       </c>
       <c r="M17">
-        <v>0.266</v>
+        <v>0.276</v>
       </c>
       <c r="N17">
-        <v>0.235</v>
+        <v>0.291</v>
       </c>
       <c r="O17">
-        <v>0.499</v>
+        <v>0.433</v>
       </c>
       <c r="P17">
-        <v>0.172</v>
+        <v>0.274</v>
       </c>
       <c r="Q17">
-        <v>12.165</v>
+        <v>11.707</v>
       </c>
       <c r="R17">
-        <v>22.283</v>
+        <v>23.354</v>
       </c>
       <c r="S17">
-        <v>2.034</v>
+        <v>2.454</v>
       </c>
       <c r="T17">
-        <v>4.109</v>
+        <v>4.881</v>
       </c>
       <c r="U17">
-        <v>3.9</v>
+        <v>4.267</v>
       </c>
       <c r="V17">
-        <v>1.613</v>
+        <v>2.458</v>
       </c>
       <c r="W17">
-        <v>0.675</v>
+        <v>0.573</v>
       </c>
       <c r="X17">
-        <v>0.335</v>
+        <v>0.442</v>
       </c>
     </row>
     <row r="18" spans="1:24">
       <c r="A18">
-        <v>823956</v>
+        <v>823958</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
@@ -2013,7 +2016,7 @@
         <v>83</v>
       </c>
       <c r="D18">
-        <v>660271</v>
+        <v>607192</v>
       </c>
       <c r="E18" t="s">
         <v>84</v>
@@ -2022,7 +2025,7 @@
         <v>85</v>
       </c>
       <c r="G18" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H18" t="s">
         <v>29</v>
@@ -2034,51 +2037,51 @@
         <v>87</v>
       </c>
       <c r="K18">
-        <v>24.161</v>
+        <v>23.481</v>
       </c>
       <c r="L18">
-        <v>6.089</v>
+        <v>5.938</v>
       </c>
       <c r="M18">
-        <v>0.488</v>
+        <v>0.413</v>
       </c>
       <c r="N18">
-        <v>0.158</v>
+        <v>0.209</v>
       </c>
       <c r="O18">
-        <v>0.354</v>
+        <v>0.379</v>
       </c>
       <c r="P18">
-        <v>0.589</v>
+        <v>0.543</v>
       </c>
       <c r="Q18">
-        <v>23.928</v>
+        <v>22.992</v>
       </c>
       <c r="R18">
-        <v>41.264</v>
+        <v>39.561</v>
       </c>
       <c r="S18">
-        <v>1.609</v>
+        <v>1.789</v>
       </c>
       <c r="T18">
-        <v>4.388</v>
+        <v>4.101</v>
       </c>
       <c r="U18">
-        <v>7.512</v>
+        <v>7.488</v>
       </c>
       <c r="V18">
-        <v>1.636</v>
+        <v>1.681</v>
       </c>
       <c r="W18">
-        <v>0.416</v>
+        <v>0.615</v>
       </c>
       <c r="X18">
-        <v>0.388</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="19" spans="1:24">
       <c r="A19">
-        <v>823956</v>
+        <v>823958</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
@@ -2087,7 +2090,7 @@
         <v>83</v>
       </c>
       <c r="D19">
-        <v>676083</v>
+        <v>645261</v>
       </c>
       <c r="E19" t="s">
         <v>88</v>
@@ -2096,7 +2099,7 @@
         <v>89</v>
       </c>
       <c r="G19" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H19" t="s">
         <v>35</v>
@@ -2108,51 +2111,51 @@
         <v>86</v>
       </c>
       <c r="K19">
-        <v>22.702</v>
+        <v>24.679</v>
       </c>
       <c r="L19">
-        <v>5.278</v>
+        <v>5.865</v>
       </c>
       <c r="M19">
-        <v>0.113</v>
+        <v>0.17</v>
       </c>
       <c r="N19">
-        <v>0.513</v>
+        <v>0.45</v>
       </c>
       <c r="O19">
-        <v>0.374</v>
+        <v>0.381</v>
       </c>
       <c r="P19">
-        <v>0.3</v>
+        <v>0.494</v>
       </c>
       <c r="Q19">
-        <v>10.158</v>
+        <v>11.774</v>
       </c>
       <c r="R19">
-        <v>20.75</v>
+        <v>24.069</v>
       </c>
       <c r="S19">
-        <v>2.853</v>
+        <v>2.736</v>
       </c>
       <c r="T19">
-        <v>5.484</v>
+        <v>5.377</v>
       </c>
       <c r="U19">
-        <v>3.867</v>
+        <v>3.896</v>
       </c>
       <c r="V19">
-        <v>1.521</v>
+        <v>2.051</v>
       </c>
       <c r="W19">
-        <v>0.918</v>
+        <v>0.808</v>
       </c>
       <c r="X19">
-        <v>0.641</v>
+        <v>0.685</v>
       </c>
     </row>
     <row r="20" spans="1:24">
       <c r="A20">
-        <v>824447</v>
+        <v>824445</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
@@ -2161,7 +2164,7 @@
         <v>90</v>
       </c>
       <c r="D20">
-        <v>607259</v>
+        <v>656876</v>
       </c>
       <c r="E20" t="s">
         <v>91</v>
@@ -2170,7 +2173,7 @@
         <v>92</v>
       </c>
       <c r="G20" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H20" t="s">
         <v>35</v>
@@ -2182,51 +2185,51 @@
         <v>94</v>
       </c>
       <c r="K20">
-        <v>19.2</v>
+        <v>21.836</v>
       </c>
       <c r="L20">
-        <v>4.642</v>
+        <v>5.58</v>
       </c>
       <c r="M20">
-        <v>0.143</v>
+        <v>0.228</v>
       </c>
       <c r="N20">
-        <v>0.264</v>
+        <v>0.28</v>
       </c>
       <c r="O20">
-        <v>0.593</v>
+        <v>0.493</v>
       </c>
       <c r="P20">
-        <v>0.118</v>
+        <v>0.448</v>
       </c>
       <c r="Q20">
-        <v>8.694</v>
+        <v>15.265</v>
       </c>
       <c r="R20">
-        <v>16.668</v>
+        <v>27.272</v>
       </c>
       <c r="S20">
-        <v>1.947</v>
+        <v>1.603</v>
       </c>
       <c r="T20">
-        <v>4.176</v>
+        <v>3.813</v>
       </c>
       <c r="U20">
-        <v>2.419</v>
+        <v>4.06</v>
       </c>
       <c r="V20">
-        <v>1.265</v>
+        <v>1.423</v>
       </c>
       <c r="W20">
-        <v>0.577</v>
+        <v>0.474</v>
       </c>
       <c r="X20">
-        <v>0.44</v>
+        <v>0.476</v>
       </c>
     </row>
     <row r="21" spans="1:24">
       <c r="A21">
-        <v>824447</v>
+        <v>824445</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
@@ -2235,7 +2238,7 @@
         <v>90</v>
       </c>
       <c r="D21">
-        <v>676440</v>
+        <v>668909</v>
       </c>
       <c r="E21" t="s">
         <v>95</v>
@@ -2244,7 +2247,7 @@
         <v>96</v>
       </c>
       <c r="G21" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H21" t="s">
         <v>29</v>
@@ -2256,51 +2259,51 @@
         <v>93</v>
       </c>
       <c r="K21">
-        <v>24.111</v>
+        <v>24.554</v>
       </c>
       <c r="L21">
-        <v>5.678</v>
+        <v>6.023</v>
       </c>
       <c r="M21">
-        <v>0.287</v>
+        <v>0.294</v>
       </c>
       <c r="N21">
-        <v>0.343</v>
+        <v>0.335</v>
       </c>
       <c r="O21">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="P21">
-        <v>0.426</v>
+        <v>0.571</v>
       </c>
       <c r="Q21">
-        <v>12.725</v>
+        <v>20.415</v>
       </c>
       <c r="R21">
-        <v>25.27</v>
+        <v>36.599</v>
       </c>
       <c r="S21">
-        <v>2.497</v>
+        <v>1.862</v>
       </c>
       <c r="T21">
-        <v>5.495</v>
+        <v>3.803</v>
       </c>
       <c r="U21">
-        <v>4.101</v>
+        <v>6.689</v>
       </c>
       <c r="V21">
-        <v>1.886</v>
+        <v>2.883</v>
       </c>
       <c r="W21">
-        <v>0.589</v>
+        <v>0.503</v>
       </c>
       <c r="X21">
-        <v>0.846</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="22" spans="1:24">
       <c r="A22">
-        <v>824526</v>
+        <v>824525</v>
       </c>
       <c r="B22" t="s">
         <v>24</v>
@@ -2309,7 +2312,7 @@
         <v>50</v>
       </c>
       <c r="D22">
-        <v>607536</v>
+        <v>608372</v>
       </c>
       <c r="E22" t="s">
         <v>97</v>
@@ -2330,51 +2333,51 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>20.395</v>
+        <v>21.144</v>
       </c>
       <c r="L22">
-        <v>4.828</v>
+        <v>4.919</v>
       </c>
       <c r="M22">
-        <v>0.137</v>
+        <v>0.161</v>
       </c>
       <c r="N22">
-        <v>0.366</v>
+        <v>0.349</v>
       </c>
       <c r="O22">
-        <v>0.497</v>
+        <v>0.49</v>
       </c>
       <c r="P22">
-        <v>0.166</v>
+        <v>0.22</v>
       </c>
       <c r="Q22">
-        <v>12.571</v>
+        <v>10.203</v>
       </c>
       <c r="R22">
-        <v>23.174</v>
+        <v>20.182</v>
       </c>
       <c r="S22">
-        <v>2.38</v>
+        <v>2.733</v>
       </c>
       <c r="T22">
-        <v>4.713</v>
+        <v>4.663</v>
       </c>
       <c r="U22">
-        <v>4.782</v>
+        <v>3.927</v>
       </c>
       <c r="V22">
-        <v>1.357</v>
+        <v>1.834</v>
       </c>
       <c r="W22">
-        <v>0.805</v>
+        <v>1.094</v>
       </c>
       <c r="X22">
-        <v>0.645</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="23" spans="1:24">
       <c r="A23">
-        <v>824526</v>
+        <v>824525</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
@@ -2383,7 +2386,7 @@
         <v>50</v>
       </c>
       <c r="D23">
-        <v>695505</v>
+        <v>682227</v>
       </c>
       <c r="E23" t="s">
         <v>101</v>
@@ -2404,60 +2407,60 @@
         <v>99</v>
       </c>
       <c r="K23">
-        <v>20.016</v>
+        <v>22.441</v>
       </c>
       <c r="L23">
-        <v>4.942</v>
+        <v>5.19</v>
       </c>
       <c r="M23">
-        <v>0.276</v>
+        <v>0.293</v>
       </c>
       <c r="N23">
-        <v>0.201</v>
+        <v>0.269</v>
       </c>
       <c r="O23">
-        <v>0.523</v>
+        <v>0.438</v>
       </c>
       <c r="P23">
-        <v>0.211</v>
+        <v>0.31</v>
       </c>
       <c r="Q23">
-        <v>17.987</v>
+        <v>11.69</v>
       </c>
       <c r="R23">
-        <v>30.675</v>
+        <v>23.164</v>
       </c>
       <c r="S23">
-        <v>1.693</v>
+        <v>2.528</v>
       </c>
       <c r="T23">
-        <v>3.546</v>
+        <v>5.044</v>
       </c>
       <c r="U23">
-        <v>6.143</v>
+        <v>4.06</v>
       </c>
       <c r="V23">
-        <v>1.691</v>
+        <v>2.003</v>
       </c>
       <c r="W23">
-        <v>0.663</v>
+        <v>0.682</v>
       </c>
       <c r="X23">
-        <v>0.428</v>
+        <v>0.488</v>
       </c>
     </row>
     <row r="24" spans="1:24">
       <c r="A24">
-        <v>824610</v>
+        <v>824608</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D24">
-        <v>663436</v>
+        <v>579328</v>
       </c>
       <c r="E24" t="s">
         <v>103</v>
@@ -2469,7 +2472,7 @@
         <v>28</v>
       </c>
       <c r="H24" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I24" t="s">
         <v>105</v>
@@ -2478,60 +2481,60 @@
         <v>106</v>
       </c>
       <c r="K24">
-        <v>23.815</v>
+        <v>21.851</v>
       </c>
       <c r="L24">
-        <v>5.437</v>
+        <v>5.154</v>
       </c>
       <c r="M24">
-        <v>0.184</v>
+        <v>0.229</v>
       </c>
       <c r="N24">
-        <v>0.46</v>
+        <v>0.243</v>
       </c>
       <c r="O24">
-        <v>0.356</v>
+        <v>0.528</v>
       </c>
       <c r="P24">
-        <v>0.351</v>
+        <v>0.319</v>
       </c>
       <c r="Q24">
-        <v>12.633</v>
+        <v>14.24</v>
       </c>
       <c r="R24">
-        <v>25.244</v>
+        <v>26.577</v>
       </c>
       <c r="S24">
-        <v>2.899</v>
+        <v>2.161</v>
       </c>
       <c r="T24">
-        <v>5.606</v>
+        <v>4.666</v>
       </c>
       <c r="U24">
-        <v>5.039</v>
+        <v>4.982</v>
       </c>
       <c r="V24">
-        <v>2.102</v>
+        <v>1.872</v>
       </c>
       <c r="W24">
-        <v>0.818</v>
+        <v>0.526</v>
       </c>
       <c r="X24">
-        <v>0.569</v>
+        <v>0.295</v>
       </c>
     </row>
     <row r="25" spans="1:24">
       <c r="A25">
-        <v>824610</v>
+        <v>824608</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D25">
-        <v>667755</v>
+        <v>607200</v>
       </c>
       <c r="E25" t="s">
         <v>107</v>
@@ -2540,10 +2543,10 @@
         <v>108</v>
       </c>
       <c r="G25" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H25" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I25" t="s">
         <v>106</v>
@@ -2552,51 +2555,51 @@
         <v>105</v>
       </c>
       <c r="K25">
-        <v>22.614</v>
+        <v>22.123</v>
       </c>
       <c r="L25">
-        <v>5.438</v>
+        <v>5.059</v>
       </c>
       <c r="M25">
-        <v>0.264</v>
+        <v>0.199</v>
       </c>
       <c r="N25">
-        <v>0.192</v>
+        <v>0.38</v>
       </c>
       <c r="O25">
-        <v>0.544</v>
+        <v>0.421</v>
       </c>
       <c r="P25">
-        <v>0.388</v>
+        <v>0.261</v>
       </c>
       <c r="Q25">
-        <v>18.754</v>
+        <v>8.919</v>
       </c>
       <c r="R25">
-        <v>33.575</v>
+        <v>19.007</v>
       </c>
       <c r="S25">
-        <v>1.76</v>
+        <v>2.554</v>
       </c>
       <c r="T25">
-        <v>3.903</v>
+        <v>4.6</v>
       </c>
       <c r="U25">
-        <v>6.469</v>
+        <v>3.085</v>
       </c>
       <c r="V25">
-        <v>2.725</v>
+        <v>2.618</v>
       </c>
       <c r="W25">
-        <v>0.383</v>
+        <v>0.712</v>
       </c>
       <c r="X25">
-        <v>0.204</v>
+        <v>0.652</v>
       </c>
     </row>
     <row r="26" spans="1:24">
       <c r="A26">
-        <v>824849</v>
+        <v>824850</v>
       </c>
       <c r="B26" t="s">
         <v>24</v>
@@ -2605,7 +2608,7 @@
         <v>109</v>
       </c>
       <c r="D26">
-        <v>669358</v>
+        <v>605135</v>
       </c>
       <c r="E26" t="s">
         <v>110</v>
@@ -2614,7 +2617,7 @@
         <v>111</v>
       </c>
       <c r="G26" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H26" t="s">
         <v>29</v>
@@ -2626,51 +2629,51 @@
         <v>113</v>
       </c>
       <c r="K26">
-        <v>22.59</v>
+        <v>19.549</v>
       </c>
       <c r="L26">
-        <v>5.123</v>
+        <v>4.314</v>
       </c>
       <c r="M26">
-        <v>0.254</v>
+        <v>0.167</v>
       </c>
       <c r="N26">
-        <v>0.312</v>
+        <v>0.3</v>
       </c>
       <c r="O26">
-        <v>0.434</v>
+        <v>0.533</v>
       </c>
       <c r="P26">
-        <v>0.294</v>
+        <v>0.09</v>
       </c>
       <c r="Q26">
-        <v>12.555</v>
+        <v>6.561</v>
       </c>
       <c r="R26">
-        <v>24.804</v>
+        <v>14.812</v>
       </c>
       <c r="S26">
-        <v>2.538</v>
+        <v>2.486</v>
       </c>
       <c r="T26">
-        <v>5.294</v>
+        <v>4.776</v>
       </c>
       <c r="U26">
-        <v>4.783</v>
+        <v>2.656</v>
       </c>
       <c r="V26">
-        <v>2.177</v>
+        <v>2.144</v>
       </c>
       <c r="W26">
-        <v>0.514</v>
+        <v>0.521</v>
       </c>
       <c r="X26">
-        <v>0.382</v>
+        <v>0.331</v>
       </c>
     </row>
     <row r="27" spans="1:24">
       <c r="A27">
-        <v>824849</v>
+        <v>824850</v>
       </c>
       <c r="B27" t="s">
         <v>24</v>
@@ -2679,7 +2682,7 @@
         <v>109</v>
       </c>
       <c r="D27">
-        <v>678906</v>
+        <v>663567</v>
       </c>
       <c r="E27" t="s">
         <v>114</v>
@@ -2688,7 +2691,7 @@
         <v>115</v>
       </c>
       <c r="G27" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H27" t="s">
         <v>35</v>
@@ -2700,51 +2703,51 @@
         <v>112</v>
       </c>
       <c r="K27">
-        <v>18.825</v>
+        <v>18.797</v>
       </c>
       <c r="L27">
-        <v>4.21</v>
+        <v>4.178</v>
       </c>
       <c r="M27">
-        <v>0.097</v>
+        <v>0.104</v>
       </c>
       <c r="N27">
-        <v>0.276</v>
+        <v>0.274</v>
       </c>
       <c r="O27">
-        <v>0.626</v>
+        <v>0.622</v>
       </c>
       <c r="P27">
-        <v>0.064</v>
+        <v>0.056</v>
       </c>
       <c r="Q27">
-        <v>10.857</v>
+        <v>8.92</v>
       </c>
       <c r="R27">
-        <v>20.697</v>
+        <v>17.823</v>
       </c>
       <c r="S27">
-        <v>2.08</v>
+        <v>2.338</v>
       </c>
       <c r="T27">
-        <v>3.875</v>
+        <v>4.085</v>
       </c>
       <c r="U27">
-        <v>4.489</v>
+        <v>3.818</v>
       </c>
       <c r="V27">
-        <v>2.494</v>
+        <v>2.346</v>
       </c>
       <c r="W27">
-        <v>0.479</v>
+        <v>0.579</v>
       </c>
       <c r="X27">
-        <v>0.245</v>
+        <v>0.243</v>
       </c>
     </row>
     <row r="28" spans="1:24">
       <c r="A28">
-        <v>824931</v>
+        <v>824930</v>
       </c>
       <c r="B28" t="s">
         <v>24</v>
@@ -2753,7 +2756,7 @@
         <v>116</v>
       </c>
       <c r="D28">
-        <v>527048</v>
+        <v>669373</v>
       </c>
       <c r="E28" t="s">
         <v>117</v>
@@ -2762,10 +2765,10 @@
         <v>118</v>
       </c>
       <c r="G28" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H28" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I28" t="s">
         <v>119</v>
@@ -2774,51 +2777,51 @@
         <v>120</v>
       </c>
       <c r="K28">
-        <v>22.399</v>
+        <v>23.723</v>
       </c>
       <c r="L28">
-        <v>5.101</v>
+        <v>5.748</v>
       </c>
       <c r="M28">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="N28">
-        <v>0.338</v>
+        <v>0.206</v>
       </c>
       <c r="O28">
-        <v>0.442</v>
+        <v>0.514</v>
       </c>
       <c r="P28">
-        <v>0.295</v>
+        <v>0.515</v>
       </c>
       <c r="Q28">
-        <v>9.392</v>
+        <v>19.037</v>
       </c>
       <c r="R28">
-        <v>19.916</v>
+        <v>34.361</v>
       </c>
       <c r="S28">
-        <v>2.614</v>
+        <v>2.213</v>
       </c>
       <c r="T28">
-        <v>4.804</v>
+        <v>5.2</v>
       </c>
       <c r="U28">
-        <v>3.317</v>
+        <v>6.671</v>
       </c>
       <c r="V28">
-        <v>2.497</v>
+        <v>1.38</v>
       </c>
       <c r="W28">
-        <v>0.713</v>
+        <v>0.632</v>
       </c>
       <c r="X28">
-        <v>0.229</v>
+        <v>0.328</v>
       </c>
     </row>
     <row r="29" spans="1:24">
       <c r="A29">
-        <v>824931</v>
+        <v>824930</v>
       </c>
       <c r="B29" t="s">
         <v>24</v>
@@ -2827,7 +2830,7 @@
         <v>116</v>
       </c>
       <c r="D29">
-        <v>663554</v>
+        <v>702275</v>
       </c>
       <c r="E29" t="s">
         <v>121</v>
@@ -2836,10 +2839,10 @@
         <v>122</v>
       </c>
       <c r="G29" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H29" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I29" t="s">
         <v>120</v>
@@ -2848,194 +2851,194 @@
         <v>119</v>
       </c>
       <c r="K29">
-        <v>22.087</v>
+        <v>23.593</v>
       </c>
       <c r="L29">
-        <v>5.213</v>
+        <v>5.275</v>
       </c>
       <c r="M29">
-        <v>0.218</v>
+        <v>0.187</v>
       </c>
       <c r="N29">
-        <v>0.277</v>
+        <v>0.45</v>
       </c>
       <c r="O29">
-        <v>0.505</v>
+        <v>0.364</v>
       </c>
       <c r="P29">
-        <v>0.315</v>
+        <v>0.337</v>
       </c>
       <c r="Q29">
-        <v>13.633</v>
+        <v>12.01</v>
       </c>
       <c r="R29">
-        <v>25.645</v>
+        <v>24.53</v>
       </c>
       <c r="S29">
-        <v>2.434</v>
+        <v>3.018</v>
       </c>
       <c r="T29">
-        <v>4.809</v>
+        <v>5.375</v>
       </c>
       <c r="U29">
-        <v>4.914</v>
+        <v>5.097</v>
       </c>
       <c r="V29">
-        <v>1.742</v>
+        <v>2.59</v>
       </c>
       <c r="W29">
-        <v>0.784</v>
+        <v>0.829</v>
       </c>
       <c r="X29">
-        <v>0.359</v>
+        <v>0.259</v>
       </c>
     </row>
     <row r="30" spans="1:24">
       <c r="A30">
-        <v>825017</v>
+        <v>825015</v>
       </c>
       <c r="B30" t="s">
         <v>24</v>
       </c>
       <c r="C30" t="s">
-        <v>43</v>
+        <v>123</v>
       </c>
       <c r="D30">
-        <v>650644</v>
+        <v>608379</v>
       </c>
       <c r="E30" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F30" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G30" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H30" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I30" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K30">
-        <v>22.754</v>
+        <v>22.355</v>
       </c>
       <c r="L30">
-        <v>5.443</v>
+        <v>5.107</v>
       </c>
       <c r="M30">
-        <v>0.255</v>
+        <v>0.193</v>
       </c>
       <c r="N30">
-        <v>0.326</v>
+        <v>0.308</v>
       </c>
       <c r="O30">
-        <v>0.419</v>
+        <v>0.499</v>
       </c>
       <c r="P30">
-        <v>0.357</v>
+        <v>0.281</v>
       </c>
       <c r="Q30">
-        <v>12.092</v>
+        <v>9.08</v>
       </c>
       <c r="R30">
-        <v>23.373</v>
+        <v>19.26</v>
       </c>
       <c r="S30">
-        <v>2.515</v>
+        <v>3.056</v>
       </c>
       <c r="T30">
-        <v>5.157</v>
+        <v>5.339</v>
       </c>
       <c r="U30">
-        <v>3.877</v>
+        <v>3.608</v>
       </c>
       <c r="V30">
-        <v>1.366</v>
+        <v>1.818</v>
       </c>
       <c r="W30">
-        <v>0.858</v>
+        <v>1.128</v>
       </c>
       <c r="X30">
-        <v>0.452</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="31" spans="1:24">
       <c r="A31">
-        <v>825017</v>
+        <v>825015</v>
       </c>
       <c r="B31" t="s">
         <v>24</v>
       </c>
       <c r="C31" t="s">
-        <v>43</v>
+        <v>123</v>
       </c>
       <c r="D31">
-        <v>663460</v>
+        <v>622663</v>
       </c>
       <c r="E31" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F31" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G31" t="s">
         <v>34</v>
       </c>
       <c r="H31" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I31" t="s">
+        <v>127</v>
+      </c>
+      <c r="J31" t="s">
         <v>126</v>
       </c>
-      <c r="J31" t="s">
-        <v>125</v>
-      </c>
       <c r="K31">
-        <v>21.681</v>
+        <v>23.216</v>
       </c>
       <c r="L31">
-        <v>5.106</v>
+        <v>5.14</v>
       </c>
       <c r="M31">
-        <v>0.201</v>
+        <v>0.254</v>
       </c>
       <c r="N31">
-        <v>0.276</v>
+        <v>0.318</v>
       </c>
       <c r="O31">
-        <v>0.523</v>
+        <v>0.428</v>
       </c>
       <c r="P31">
-        <v>0.295</v>
+        <v>0.274</v>
       </c>
       <c r="Q31">
-        <v>14.107</v>
+        <v>9.666</v>
       </c>
       <c r="R31">
-        <v>26.269</v>
+        <v>20.87</v>
       </c>
       <c r="S31">
-        <v>2.341</v>
+        <v>3.084</v>
       </c>
       <c r="T31">
-        <v>4.583</v>
+        <v>5.387</v>
       </c>
       <c r="U31">
-        <v>5.196</v>
+        <v>4.026</v>
       </c>
       <c r="V31">
-        <v>1.926</v>
+        <v>2.627</v>
       </c>
       <c r="W31">
-        <v>0.776</v>
+        <v>0.787</v>
       </c>
       <c r="X31">
-        <v>0.228</v>
+        <v>0.662</v>
       </c>
     </row>
   </sheetData>

--- a/data/BallparkPal_Pitchers.xlsx
+++ b/data/BallparkPal_Pitchers.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="100">
   <si>
     <t>GamePk</t>
   </si>
@@ -89,229 +89,145 @@
     <t>StolenBasesAllowed</t>
   </si>
   <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>3:07</t>
-  </si>
-  <si>
-    <t>Eric Lauer</t>
-  </si>
-  <si>
-    <t>Lauer</t>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>Hunter Dobbins</t>
+  </si>
+  <si>
+    <t>Dobbins</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>STL</t>
+  </si>
+  <si>
+    <t>PIT</t>
+  </si>
+  <si>
+    <t>Paul Skenes</t>
+  </si>
+  <si>
+    <t>Skenes</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>5:35</t>
+  </si>
+  <si>
+    <t>Adrian Houser</t>
+  </si>
+  <si>
+    <t>Houser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF </t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>Andrew Painter</t>
+  </si>
+  <si>
+    <t>Painter</t>
+  </si>
+  <si>
+    <t>Cristopher Sanchez</t>
+  </si>
+  <si>
+    <t>Sanchez</t>
   </si>
   <si>
     <t>L</t>
   </si>
   <si>
-    <t>H</t>
+    <t>Logan Webb</t>
+  </si>
+  <si>
+    <t>Webb</t>
+  </si>
+  <si>
+    <t>1:10</t>
+  </si>
+  <si>
+    <t>Miles Mikolas</t>
+  </si>
+  <si>
+    <t>Mikolas</t>
+  </si>
+  <si>
+    <t>WAS</t>
+  </si>
+  <si>
+    <t>NYM</t>
+  </si>
+  <si>
+    <t>Freddy Peralta</t>
+  </si>
+  <si>
+    <t>Peralta</t>
+  </si>
+  <si>
+    <t>7:40</t>
+  </si>
+  <si>
+    <t>Kevin Gausman</t>
+  </si>
+  <si>
+    <t>Gausman</t>
   </si>
   <si>
     <t>TOR</t>
   </si>
   <si>
-    <t>BOS</t>
-  </si>
-  <si>
-    <t>Brayan Bello</t>
-  </si>
-  <si>
-    <t>Bello</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>2:35</t>
-  </si>
-  <si>
-    <t>Nathan Eovaldi</t>
-  </si>
-  <si>
-    <t>Eovaldi</t>
-  </si>
-  <si>
-    <t>TEX</t>
-  </si>
-  <si>
-    <t>NYY</t>
-  </si>
-  <si>
-    <t>Elmer Rodriguez</t>
-  </si>
-  <si>
-    <t>Rodriguez</t>
-  </si>
-  <si>
-    <t>4:10</t>
-  </si>
-  <si>
-    <t>Jameson Taillon</t>
-  </si>
-  <si>
-    <t>Taillon</t>
-  </si>
-  <si>
-    <t>CHC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SD </t>
-  </si>
-  <si>
-    <t>Matt Waldron</t>
-  </si>
-  <si>
-    <t>Waldron</t>
-  </si>
-  <si>
-    <t>6:40</t>
-  </si>
-  <si>
-    <t>Andre Pallante</t>
-  </si>
-  <si>
-    <t>Pallante</t>
-  </si>
-  <si>
-    <t>STL</t>
-  </si>
-  <si>
-    <t>PIT</t>
-  </si>
-  <si>
-    <t>Bubba Chandler</t>
-  </si>
-  <si>
-    <t>Chandler</t>
-  </si>
-  <si>
-    <t>Cristopher Sanchez</t>
-  </si>
-  <si>
-    <t>Sanchez</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF </t>
-  </si>
-  <si>
-    <t>Logan Webb</t>
-  </si>
-  <si>
-    <t>Webb</t>
-  </si>
-  <si>
-    <t>7:10</t>
-  </si>
-  <si>
-    <t>David Peterson</t>
-  </si>
-  <si>
-    <t>Peterson</t>
-  </si>
-  <si>
-    <t>NYM</t>
-  </si>
-  <si>
-    <t>WAS</t>
-  </si>
-  <si>
-    <t>Cade Cavalli</t>
-  </si>
-  <si>
-    <t>Cavalli</t>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>Bailey Ober</t>
+  </si>
+  <si>
+    <t>Ober</t>
   </si>
   <si>
     <t>1:40</t>
   </si>
   <si>
-    <t>George Kirby</t>
-  </si>
-  <si>
-    <t>Kirby</t>
-  </si>
-  <si>
-    <t>SEA</t>
-  </si>
-  <si>
-    <t>MIN</t>
-  </si>
-  <si>
-    <t>Taj Bradley</t>
-  </si>
-  <si>
-    <t>Bradley</t>
-  </si>
-  <si>
-    <t>7:40</t>
-  </si>
-  <si>
-    <t>Eduardo Rodriguez</t>
+    <t>Brandon Woodruff</t>
+  </si>
+  <si>
+    <t>Woodruff</t>
+  </si>
+  <si>
+    <t>MIL</t>
   </si>
   <si>
     <t>ARI</t>
   </si>
   <si>
-    <t>MIL</t>
-  </si>
-  <si>
-    <t>Brandon Sproat</t>
-  </si>
-  <si>
-    <t>Sproat</t>
-  </si>
-  <si>
-    <t>3:10</t>
-  </si>
-  <si>
-    <t>Tyler Glasnow</t>
-  </si>
-  <si>
-    <t>Glasnow</t>
-  </si>
-  <si>
-    <t>LAD</t>
-  </si>
-  <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>Sandy Alcantara</t>
-  </si>
-  <si>
-    <t>Alcantara</t>
-  </si>
-  <si>
-    <t>1:10</t>
-  </si>
-  <si>
-    <t>Drew Rasmussen</t>
-  </si>
-  <si>
-    <t>Rasmussen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB </t>
-  </si>
-  <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>Gavin Williams</t>
-  </si>
-  <si>
-    <t>Williams</t>
-  </si>
-  <si>
-    <t>Tomoyuki Sugano</t>
-  </si>
-  <si>
-    <t>Sugano</t>
+    <t>Michael Soroka</t>
+  </si>
+  <si>
+    <t>Soroka</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>Michael Lorenzen</t>
+  </si>
+  <si>
+    <t>Lorenzen</t>
   </si>
   <si>
     <t>COL</t>
@@ -320,31 +236,10 @@
     <t>CIN</t>
   </si>
   <si>
-    <t>Brandon Williamson</t>
-  </si>
-  <si>
-    <t>Williamson</t>
-  </si>
-  <si>
-    <t>Yusei Kikuchi</t>
-  </si>
-  <si>
-    <t>Kikuchi</t>
-  </si>
-  <si>
-    <t>LAA</t>
-  </si>
-  <si>
-    <t>CHW</t>
-  </si>
-  <si>
-    <t>Erick Fedde</t>
-  </si>
-  <si>
-    <t>Fedde</t>
-  </si>
-  <si>
-    <t>6:35</t>
+    <t>Andrew Abbott</t>
+  </si>
+  <si>
+    <t>Abbott</t>
   </si>
   <si>
     <t>Chris Bassitt</t>
@@ -365,13 +260,28 @@
     <t>Lambert</t>
   </si>
   <si>
-    <t>7:15</t>
-  </si>
-  <si>
-    <t>Tarik Skubal</t>
-  </si>
-  <si>
-    <t>Skubal</t>
+    <t>4:05</t>
+  </si>
+  <si>
+    <t>Lance McCullers Jr.</t>
+  </si>
+  <si>
+    <t>McCullers Jr.</t>
+  </si>
+  <si>
+    <t>Brandon Young</t>
+  </si>
+  <si>
+    <t>Young</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>Framber Valdez</t>
+  </si>
+  <si>
+    <t>Valdez</t>
   </si>
   <si>
     <t>DET</t>
@@ -380,31 +290,31 @@
     <t>ATL</t>
   </si>
   <si>
-    <t>JR Ritchie</t>
-  </si>
-  <si>
-    <t>Ritchie</t>
-  </si>
-  <si>
-    <t>9:40</t>
-  </si>
-  <si>
-    <t>Michael Wacha</t>
-  </si>
-  <si>
-    <t>Wacha</t>
+    <t>Bryce Elder</t>
+  </si>
+  <si>
+    <t>Elder</t>
+  </si>
+  <si>
+    <t>3:05</t>
+  </si>
+  <si>
+    <t>Jeffrey Springs</t>
+  </si>
+  <si>
+    <t>Springs</t>
+  </si>
+  <si>
+    <t>ATH</t>
   </si>
   <si>
     <t xml:space="preserve">KC </t>
   </si>
   <si>
-    <t>ATH</t>
-  </si>
-  <si>
-    <t>Luis Severino</t>
-  </si>
-  <si>
-    <t>Severino</t>
+    <t>Noah Cameron</t>
+  </si>
+  <si>
+    <t>Cameron</t>
   </si>
 </sst>
 </file>
@@ -744,7 +654,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:24">
@@ -823,7 +733,7 @@
     </row>
     <row r="2" spans="1:24">
       <c r="A2">
-        <v>822821</v>
+        <v>823391</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
@@ -832,7 +742,7 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>641778</v>
+        <v>690928</v>
       </c>
       <c r="E2" t="s">
         <v>26</v>
@@ -853,51 +763,51 @@
         <v>31</v>
       </c>
       <c r="K2">
-        <v>19.981</v>
+        <v>20.027</v>
       </c>
       <c r="L2">
-        <v>4.68</v>
+        <v>4.714</v>
       </c>
       <c r="M2">
+        <v>0.1</v>
+      </c>
+      <c r="N2">
+        <v>0.419</v>
+      </c>
+      <c r="O2">
+        <v>0.481</v>
+      </c>
+      <c r="P2">
+        <v>0.174</v>
+      </c>
+      <c r="Q2">
+        <v>9.675</v>
+      </c>
+      <c r="R2">
+        <v>18.928</v>
+      </c>
+      <c r="S2">
+        <v>2.104</v>
+      </c>
+      <c r="T2">
+        <v>4.467</v>
+      </c>
+      <c r="U2">
+        <v>3.266</v>
+      </c>
+      <c r="V2">
+        <v>1.632</v>
+      </c>
+      <c r="W2">
+        <v>0.486</v>
+      </c>
+      <c r="X2">
         <v>0.243</v>
-      </c>
-      <c r="N2">
-        <v>0.271</v>
-      </c>
-      <c r="O2">
-        <v>0.486</v>
-      </c>
-      <c r="P2">
-        <v>0.143</v>
-      </c>
-      <c r="Q2">
-        <v>10.778</v>
-      </c>
-      <c r="R2">
-        <v>20.436</v>
-      </c>
-      <c r="S2">
-        <v>2.299</v>
-      </c>
-      <c r="T2">
-        <v>4.575</v>
-      </c>
-      <c r="U2">
-        <v>3.753</v>
-      </c>
-      <c r="V2">
-        <v>1.482</v>
-      </c>
-      <c r="W2">
-        <v>0.768</v>
-      </c>
-      <c r="X2">
-        <v>0.39</v>
       </c>
     </row>
     <row r="3" spans="1:24">
       <c r="A3">
-        <v>822821</v>
+        <v>823391</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
@@ -906,7 +816,7 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>678394</v>
+        <v>694973</v>
       </c>
       <c r="E3" t="s">
         <v>32</v>
@@ -915,10 +825,10 @@
         <v>33</v>
       </c>
       <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
         <v>34</v>
-      </c>
-      <c r="H3" t="s">
-        <v>35</v>
       </c>
       <c r="I3" t="s">
         <v>31</v>
@@ -927,510 +837,510 @@
         <v>30</v>
       </c>
       <c r="K3">
-        <v>21.685</v>
+        <v>23.053</v>
       </c>
       <c r="L3">
-        <v>4.889</v>
+        <v>5.949</v>
       </c>
       <c r="M3">
-        <v>0.162</v>
+        <v>0.416</v>
       </c>
       <c r="N3">
-        <v>0.381</v>
+        <v>0.174</v>
       </c>
       <c r="O3">
-        <v>0.457</v>
+        <v>0.41</v>
       </c>
       <c r="P3">
-        <v>0.223</v>
+        <v>0.564</v>
       </c>
       <c r="Q3">
-        <v>6.408</v>
+        <v>21.761</v>
       </c>
       <c r="R3">
-        <v>15.291</v>
+        <v>37.35</v>
       </c>
       <c r="S3">
-        <v>3.002</v>
+        <v>1.387</v>
       </c>
       <c r="T3">
-        <v>5.491</v>
+        <v>3.579</v>
       </c>
       <c r="U3">
-        <v>2.587</v>
+        <v>6.304</v>
       </c>
       <c r="V3">
-        <v>1.877</v>
+        <v>1.727</v>
       </c>
       <c r="W3">
-        <v>0.954</v>
+        <v>0.458</v>
       </c>
       <c r="X3">
-        <v>0.381</v>
+        <v>0.321</v>
       </c>
     </row>
     <row r="4" spans="1:24">
       <c r="A4">
-        <v>822907</v>
+        <v>823471</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4">
+        <v>605288</v>
+      </c>
+      <c r="E4" t="s">
         <v>36</v>
       </c>
-      <c r="D4">
-        <v>543135</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>37</v>
       </c>
-      <c r="F4" t="s">
-        <v>38</v>
-      </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H4" t="s">
         <v>29</v>
       </c>
       <c r="I4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" t="s">
         <v>39</v>
       </c>
-      <c r="J4" t="s">
-        <v>40</v>
-      </c>
       <c r="K4">
-        <v>25.067</v>
+        <v>22.325</v>
       </c>
       <c r="L4">
-        <v>6.083</v>
+        <v>4.94</v>
       </c>
       <c r="M4">
-        <v>0.377</v>
+        <v>0.164</v>
       </c>
       <c r="N4">
-        <v>0.277</v>
+        <v>0.395</v>
       </c>
       <c r="O4">
-        <v>0.346</v>
+        <v>0.441</v>
       </c>
       <c r="P4">
-        <v>0.511</v>
+        <v>0.245</v>
       </c>
       <c r="Q4">
-        <v>17.934</v>
+        <v>7.859</v>
       </c>
       <c r="R4">
-        <v>32.951</v>
+        <v>18.001</v>
       </c>
       <c r="S4">
-        <v>2.601</v>
+        <v>3.039</v>
       </c>
       <c r="T4">
-        <v>5.273</v>
+        <v>5.815</v>
       </c>
       <c r="U4">
-        <v>6.066</v>
+        <v>3.446</v>
       </c>
       <c r="V4">
-        <v>1.827</v>
+        <v>2.063</v>
       </c>
       <c r="W4">
-        <v>0.899</v>
+        <v>0.644</v>
       </c>
       <c r="X4">
-        <v>0.445</v>
+        <v>0.705</v>
       </c>
     </row>
     <row r="5" spans="1:24">
       <c r="A5">
-        <v>822907</v>
+        <v>823471</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5">
-        <v>695684</v>
+        <v>691725</v>
       </c>
       <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
         <v>41</v>
       </c>
-      <c r="F5" t="s">
-        <v>42</v>
-      </c>
       <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
         <v>34</v>
       </c>
-      <c r="H5" t="s">
-        <v>35</v>
-      </c>
       <c r="I5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K5">
-        <v>18.944</v>
+        <v>22.136</v>
       </c>
       <c r="L5">
-        <v>4.244</v>
+        <v>5.026</v>
       </c>
       <c r="M5">
-        <v>0.094</v>
+        <v>0.311</v>
       </c>
       <c r="N5">
-        <v>0.345</v>
+        <v>0.25</v>
       </c>
       <c r="O5">
-        <v>0.561</v>
+        <v>0.439</v>
       </c>
       <c r="P5">
-        <v>0.064</v>
+        <v>0.27</v>
       </c>
       <c r="Q5">
-        <v>8.335</v>
+        <v>11.33</v>
       </c>
       <c r="R5">
-        <v>17.008</v>
+        <v>22.735</v>
       </c>
       <c r="S5">
-        <v>2.476</v>
+        <v>2.386</v>
       </c>
       <c r="T5">
-        <v>4.668</v>
+        <v>5.042</v>
       </c>
       <c r="U5">
-        <v>3.628</v>
+        <v>3.955</v>
       </c>
       <c r="V5">
-        <v>1.824</v>
+        <v>2.24</v>
       </c>
       <c r="W5">
-        <v>0.612</v>
+        <v>0.584</v>
       </c>
       <c r="X5">
-        <v>0.339</v>
+        <v>0.193</v>
       </c>
     </row>
     <row r="6" spans="1:24">
       <c r="A6">
-        <v>823312</v>
+        <v>823472</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6">
+        <v>650911</v>
+      </c>
+      <c r="E6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" t="s">
         <v>43</v>
       </c>
-      <c r="D6">
-        <v>592791</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>44</v>
       </c>
-      <c r="F6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>34</v>
       </c>
-      <c r="H6" t="s">
-        <v>35</v>
-      </c>
       <c r="I6" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="J6" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K6">
-        <v>22.162</v>
+        <v>24.607</v>
       </c>
       <c r="L6">
-        <v>5.256</v>
+        <v>6.039</v>
       </c>
       <c r="M6">
-        <v>0.223</v>
+        <v>0.376</v>
       </c>
       <c r="N6">
-        <v>0.261</v>
+        <v>0.259</v>
       </c>
       <c r="O6">
-        <v>0.516</v>
+        <v>0.366</v>
       </c>
       <c r="P6">
-        <v>0.319</v>
+        <v>0.565</v>
       </c>
       <c r="Q6">
-        <v>12.617</v>
+        <v>19.901</v>
       </c>
       <c r="R6">
-        <v>24.064</v>
+        <v>35.916</v>
       </c>
       <c r="S6">
-        <v>2.49</v>
+        <v>1.946</v>
       </c>
       <c r="T6">
-        <v>4.641</v>
+        <v>5.442</v>
       </c>
       <c r="U6">
-        <v>4.385</v>
+        <v>6.375</v>
       </c>
       <c r="V6">
-        <v>1.867</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>0.828</v>
+        <v>0.445</v>
       </c>
       <c r="X6">
-        <v>0.438</v>
+        <v>0.244</v>
       </c>
     </row>
     <row r="7" spans="1:24">
       <c r="A7">
-        <v>823312</v>
+        <v>823472</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D7">
-        <v>663362</v>
+        <v>657277</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H7" t="s">
         <v>29</v>
       </c>
       <c r="I7" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="J7" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="K7">
-        <v>23.261</v>
+        <v>23.799</v>
       </c>
       <c r="L7">
-        <v>5.087</v>
+        <v>5.632</v>
       </c>
       <c r="M7">
-        <v>0.226</v>
+        <v>0.197</v>
       </c>
       <c r="N7">
-        <v>0.384</v>
+        <v>0.398</v>
       </c>
       <c r="O7">
-        <v>0.39</v>
+        <v>0.405</v>
       </c>
       <c r="P7">
-        <v>0.274</v>
+        <v>0.469</v>
       </c>
       <c r="Q7">
-        <v>9.75</v>
+        <v>14.158</v>
       </c>
       <c r="R7">
-        <v>21.217</v>
+        <v>27.476</v>
       </c>
       <c r="S7">
-        <v>2.999</v>
+        <v>2.388</v>
       </c>
       <c r="T7">
-        <v>5.1</v>
+        <v>5.394</v>
       </c>
       <c r="U7">
-        <v>4.166</v>
+        <v>4.894</v>
       </c>
       <c r="V7">
-        <v>3.14</v>
+        <v>1.844</v>
       </c>
       <c r="W7">
-        <v>0.758</v>
+        <v>0.496</v>
       </c>
       <c r="X7">
-        <v>0.573</v>
+        <v>0.642</v>
       </c>
     </row>
     <row r="8" spans="1:24">
       <c r="A8">
-        <v>823392</v>
+        <v>823634</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
       </c>
       <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8">
+        <v>571945</v>
+      </c>
+      <c r="E8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" t="s">
         <v>50</v>
       </c>
-      <c r="D8">
-        <v>669467</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="J8" t="s">
         <v>51</v>
       </c>
-      <c r="F8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8" t="s">
-        <v>53</v>
-      </c>
-      <c r="J8" t="s">
-        <v>54</v>
-      </c>
       <c r="K8">
-        <v>22.341</v>
+        <v>21.174</v>
       </c>
       <c r="L8">
-        <v>5.047</v>
+        <v>5.106</v>
       </c>
       <c r="M8">
-        <v>0.148</v>
+        <v>0.161</v>
       </c>
       <c r="N8">
-        <v>0.409</v>
+        <v>0.37</v>
       </c>
       <c r="O8">
-        <v>0.443</v>
+        <v>0.469</v>
       </c>
       <c r="P8">
-        <v>0.26</v>
+        <v>0.267</v>
       </c>
       <c r="Q8">
-        <v>8.918</v>
+        <v>10.485</v>
       </c>
       <c r="R8">
-        <v>19.32</v>
+        <v>20.293</v>
       </c>
       <c r="S8">
-        <v>2.654</v>
+        <v>2.249</v>
       </c>
       <c r="T8">
-        <v>5.032</v>
+        <v>4.684</v>
       </c>
       <c r="U8">
-        <v>3.406</v>
+        <v>3.229</v>
       </c>
       <c r="V8">
-        <v>2.526</v>
+        <v>1.34</v>
       </c>
       <c r="W8">
-        <v>0.501</v>
+        <v>0.783</v>
       </c>
       <c r="X8">
-        <v>0.508</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="9" spans="1:24">
       <c r="A9">
-        <v>823392</v>
+        <v>823634</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
       </c>
       <c r="C9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9">
+        <v>642547</v>
+      </c>
+      <c r="E9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" t="s">
         <v>50</v>
       </c>
-      <c r="D9">
-        <v>696149</v>
-      </c>
-      <c r="E9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" t="s">
-        <v>29</v>
-      </c>
-      <c r="I9" t="s">
-        <v>54</v>
-      </c>
-      <c r="J9" t="s">
-        <v>53</v>
-      </c>
       <c r="K9">
-        <v>23.008</v>
+        <v>23.263</v>
       </c>
       <c r="L9">
-        <v>5.567</v>
+        <v>5.633</v>
       </c>
       <c r="M9">
-        <v>0.365</v>
+        <v>0.347</v>
       </c>
       <c r="N9">
-        <v>0.22</v>
+        <v>0.255</v>
       </c>
       <c r="O9">
-        <v>0.415</v>
+        <v>0.398</v>
       </c>
       <c r="P9">
-        <v>0.431</v>
+        <v>0.447</v>
       </c>
       <c r="Q9">
-        <v>16.239</v>
+        <v>18.12</v>
       </c>
       <c r="R9">
-        <v>29.794</v>
+        <v>32.631</v>
       </c>
       <c r="S9">
-        <v>1.952</v>
+        <v>2.007</v>
       </c>
       <c r="T9">
-        <v>4.171</v>
+        <v>4.281</v>
       </c>
       <c r="U9">
-        <v>5.011</v>
+        <v>5.961</v>
       </c>
       <c r="V9">
-        <v>2.306</v>
+        <v>2.181</v>
       </c>
       <c r="W9">
-        <v>0.537</v>
+        <v>0.615</v>
       </c>
       <c r="X9">
-        <v>0.49</v>
+        <v>0.792</v>
       </c>
     </row>
     <row r="10" spans="1:24">
       <c r="A10">
-        <v>823471</v>
+        <v>823714</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D10">
-        <v>650911</v>
+        <v>592332</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G10" t="s">
         <v>28</v>
@@ -1439,1606 +1349,1014 @@
         <v>29</v>
       </c>
       <c r="I10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K10">
-        <v>24.559</v>
+        <v>22.526</v>
       </c>
       <c r="L10">
-        <v>5.987</v>
+        <v>5.478</v>
       </c>
       <c r="M10">
-        <v>0.377</v>
+        <v>0.229</v>
       </c>
       <c r="N10">
-        <v>0.252</v>
+        <v>0.276</v>
       </c>
       <c r="O10">
-        <v>0.371</v>
+        <v>0.495</v>
       </c>
       <c r="P10">
-        <v>0.562</v>
+        <v>0.426</v>
       </c>
       <c r="Q10">
-        <v>19.441</v>
+        <v>16.849</v>
       </c>
       <c r="R10">
-        <v>35.362</v>
+        <v>30.467</v>
       </c>
       <c r="S10">
-        <v>2.058</v>
+        <v>2.133</v>
       </c>
       <c r="T10">
-        <v>5.488</v>
+        <v>4.743</v>
       </c>
       <c r="U10">
-        <v>6.354</v>
+        <v>5.784</v>
       </c>
       <c r="V10">
-        <v>1.472</v>
+        <v>1.438</v>
       </c>
       <c r="W10">
-        <v>0.522</v>
+        <v>0.678</v>
       </c>
       <c r="X10">
-        <v>0.244</v>
+        <v>0.345</v>
       </c>
     </row>
     <row r="11" spans="1:24">
       <c r="A11">
-        <v>823471</v>
+        <v>823714</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D11">
-        <v>657277</v>
+        <v>641927</v>
       </c>
       <c r="E11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" t="s">
         <v>34</v>
       </c>
-      <c r="H11" t="s">
-        <v>35</v>
-      </c>
       <c r="I11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K11">
-        <v>23.859</v>
+        <v>23.627</v>
       </c>
       <c r="L11">
-        <v>5.597</v>
+        <v>5.64</v>
       </c>
       <c r="M11">
-        <v>0.188</v>
+        <v>0.262</v>
       </c>
       <c r="N11">
-        <v>0.397</v>
+        <v>0.354</v>
       </c>
       <c r="O11">
-        <v>0.415</v>
+        <v>0.384</v>
       </c>
       <c r="P11">
-        <v>0.438</v>
+        <v>0.424</v>
       </c>
       <c r="Q11">
-        <v>13.428</v>
+        <v>13.146</v>
       </c>
       <c r="R11">
-        <v>26.481</v>
+        <v>25.394</v>
       </c>
       <c r="S11">
-        <v>2.648</v>
+        <v>2.393</v>
       </c>
       <c r="T11">
-        <v>5.559</v>
+        <v>5.283</v>
       </c>
       <c r="U11">
-        <v>4.918</v>
+        <v>4.129</v>
       </c>
       <c r="V11">
-        <v>1.884</v>
+        <v>1.513</v>
       </c>
       <c r="W11">
-        <v>0.603</v>
+        <v>0.697</v>
       </c>
       <c r="X11">
-        <v>0.643</v>
+        <v>0.344</v>
       </c>
     </row>
     <row r="12" spans="1:24">
       <c r="A12">
-        <v>823633</v>
+        <v>823795</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
       </c>
       <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12">
+        <v>605540</v>
+      </c>
+      <c r="E12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" t="s">
         <v>63</v>
-      </c>
-      <c r="D12">
-        <v>656849</v>
-      </c>
-      <c r="E12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" t="s">
-        <v>65</v>
       </c>
       <c r="G12" t="s">
         <v>28</v>
       </c>
       <c r="H12" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K12">
-        <v>21.448</v>
+        <v>23.534</v>
       </c>
       <c r="L12">
-        <v>4.832</v>
+        <v>5.904</v>
       </c>
       <c r="M12">
-        <v>0.224</v>
+        <v>0.393</v>
       </c>
       <c r="N12">
-        <v>0.321</v>
+        <v>0.234</v>
       </c>
       <c r="O12">
-        <v>0.455</v>
+        <v>0.374</v>
       </c>
       <c r="P12">
-        <v>0.233</v>
+        <v>0.515</v>
       </c>
       <c r="Q12">
-        <v>11.386</v>
+        <v>17.369</v>
       </c>
       <c r="R12">
-        <v>22.8</v>
+        <v>31.125</v>
       </c>
       <c r="S12">
-        <v>2.402</v>
+        <v>2.142</v>
       </c>
       <c r="T12">
-        <v>5.137</v>
+        <v>4.653</v>
       </c>
       <c r="U12">
-        <v>4.411</v>
+        <v>5.14</v>
       </c>
       <c r="V12">
-        <v>2.197</v>
+        <v>1.189</v>
       </c>
       <c r="W12">
-        <v>0.439</v>
+        <v>0.9</v>
       </c>
       <c r="X12">
-        <v>0.749</v>
+        <v>0.457</v>
       </c>
     </row>
     <row r="13" spans="1:24">
       <c r="A13">
-        <v>823633</v>
+        <v>823795</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D13">
-        <v>676917</v>
+        <v>647336</v>
       </c>
       <c r="E13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G13" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H13" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K13">
-        <v>20.94</v>
+        <v>18.701</v>
       </c>
       <c r="L13">
-        <v>4.868</v>
+        <v>4.219</v>
       </c>
       <c r="M13">
-        <v>0.168</v>
+        <v>0.087</v>
       </c>
       <c r="N13">
-        <v>0.288</v>
+        <v>0.357</v>
       </c>
       <c r="O13">
-        <v>0.544</v>
+        <v>0.556</v>
       </c>
       <c r="P13">
-        <v>0.209</v>
+        <v>0.063</v>
       </c>
       <c r="Q13">
-        <v>11.95</v>
+        <v>11.73</v>
       </c>
       <c r="R13">
-        <v>22.909</v>
+        <v>21.891</v>
       </c>
       <c r="S13">
-        <v>2.136</v>
+        <v>2.177</v>
       </c>
       <c r="T13">
-        <v>4.453</v>
+        <v>3.818</v>
       </c>
       <c r="U13">
-        <v>4.289</v>
+        <v>4.996</v>
       </c>
       <c r="V13">
-        <v>2.185</v>
+        <v>2.432</v>
       </c>
       <c r="W13">
-        <v>0.554</v>
+        <v>0.628</v>
       </c>
       <c r="X13">
-        <v>0.511</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="14" spans="1:24">
       <c r="A14">
-        <v>823717</v>
+        <v>824524</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
       </c>
       <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14">
+        <v>547179</v>
+      </c>
+      <c r="E14" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" t="s">
         <v>70</v>
       </c>
-      <c r="D14">
-        <v>669923</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="G14" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" t="s">
         <v>71</v>
       </c>
-      <c r="F14" t="s">
+      <c r="J14" t="s">
         <v>72</v>
       </c>
-      <c r="G14" t="s">
-        <v>34</v>
-      </c>
-      <c r="H14" t="s">
-        <v>35</v>
-      </c>
-      <c r="I14" t="s">
-        <v>73</v>
-      </c>
-      <c r="J14" t="s">
-        <v>74</v>
-      </c>
       <c r="K14">
-        <v>23.173</v>
+        <v>21.223</v>
       </c>
       <c r="L14">
-        <v>5.492</v>
+        <v>4.879</v>
       </c>
       <c r="M14">
-        <v>0.231</v>
+        <v>0.174</v>
       </c>
       <c r="N14">
-        <v>0.286</v>
+        <v>0.291</v>
       </c>
       <c r="O14">
-        <v>0.483</v>
+        <v>0.535</v>
       </c>
       <c r="P14">
-        <v>0.415</v>
+        <v>0.222</v>
       </c>
       <c r="Q14">
-        <v>13.405</v>
+        <v>10.446</v>
       </c>
       <c r="R14">
-        <v>25.92</v>
+        <v>20.828</v>
       </c>
       <c r="S14">
-        <v>2.318</v>
+        <v>2.466</v>
       </c>
       <c r="T14">
-        <v>5.074</v>
+        <v>4.85</v>
       </c>
       <c r="U14">
-        <v>4.45</v>
+        <v>3.886</v>
       </c>
       <c r="V14">
-        <v>1.845</v>
+        <v>1.935</v>
       </c>
       <c r="W14">
-        <v>0.635</v>
+        <v>0.685</v>
       </c>
       <c r="X14">
-        <v>0.481</v>
+        <v>0.555</v>
       </c>
     </row>
     <row r="15" spans="1:24">
       <c r="A15">
-        <v>823717</v>
+        <v>824524</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D15">
-        <v>671737</v>
+        <v>671096</v>
       </c>
       <c r="E15" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F15" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" t="s">
         <v>34</v>
       </c>
-      <c r="H15" t="s">
-        <v>29</v>
-      </c>
       <c r="I15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K15">
-        <v>24.022</v>
+        <v>23.608</v>
       </c>
       <c r="L15">
-        <v>5.565</v>
+        <v>5.463</v>
       </c>
       <c r="M15">
-        <v>0.266</v>
+        <v>0.279</v>
       </c>
       <c r="N15">
-        <v>0.342</v>
+        <v>0.32</v>
       </c>
       <c r="O15">
-        <v>0.392</v>
+        <v>0.4</v>
       </c>
       <c r="P15">
-        <v>0.427</v>
+        <v>0.365</v>
       </c>
       <c r="Q15">
-        <v>16.546</v>
+        <v>13.072</v>
       </c>
       <c r="R15">
-        <v>31.09</v>
+        <v>25.642</v>
       </c>
       <c r="S15">
-        <v>2.438</v>
+        <v>2.819</v>
       </c>
       <c r="T15">
-        <v>4.571</v>
+        <v>5.906</v>
       </c>
       <c r="U15">
-        <v>6.134</v>
+        <v>4.857</v>
       </c>
       <c r="V15">
-        <v>2.84</v>
+        <v>1.471</v>
       </c>
       <c r="W15">
-        <v>0.672</v>
+        <v>0.838</v>
       </c>
       <c r="X15">
-        <v>0.304</v>
+        <v>0.606</v>
       </c>
     </row>
     <row r="16" spans="1:24">
       <c r="A16">
-        <v>823796</v>
+        <v>824848</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="D16">
-        <v>593958</v>
+        <v>605135</v>
       </c>
       <c r="E16" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F16" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="G16" t="s">
         <v>28</v>
       </c>
       <c r="H16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K16">
-        <v>22.61</v>
+        <v>19.666</v>
       </c>
       <c r="L16">
-        <v>5.094</v>
+        <v>4.339</v>
       </c>
       <c r="M16">
-        <v>0.175</v>
+        <v>0.176</v>
       </c>
       <c r="N16">
-        <v>0.37</v>
+        <v>0.306</v>
       </c>
       <c r="O16">
-        <v>0.455</v>
+        <v>0.519</v>
       </c>
       <c r="P16">
-        <v>0.299</v>
+        <v>0.09</v>
       </c>
       <c r="Q16">
-        <v>8.705</v>
+        <v>6.741</v>
       </c>
       <c r="R16">
-        <v>19.246</v>
+        <v>15.122</v>
       </c>
       <c r="S16">
-        <v>2.83</v>
+        <v>2.456</v>
       </c>
       <c r="T16">
-        <v>5.283</v>
+        <v>4.797</v>
       </c>
       <c r="U16">
-        <v>3.402</v>
+        <v>2.687</v>
       </c>
       <c r="V16">
-        <v>2.391</v>
+        <v>2.18</v>
       </c>
       <c r="W16">
-        <v>0.644</v>
+        <v>0.478</v>
       </c>
       <c r="X16">
-        <v>0.651</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="17" spans="1:24">
       <c r="A17">
-        <v>823796</v>
+        <v>824848</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="D17">
-        <v>687075</v>
+        <v>663567</v>
       </c>
       <c r="E17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H17" t="s">
         <v>29</v>
       </c>
       <c r="I17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K17">
-        <v>22.172</v>
+        <v>18.835</v>
       </c>
       <c r="L17">
-        <v>5.055</v>
+        <v>4.2</v>
       </c>
       <c r="M17">
-        <v>0.276</v>
+        <v>0.095</v>
       </c>
       <c r="N17">
-        <v>0.291</v>
+        <v>0.285</v>
       </c>
       <c r="O17">
-        <v>0.433</v>
+        <v>0.62</v>
       </c>
       <c r="P17">
-        <v>0.274</v>
+        <v>0.057</v>
       </c>
       <c r="Q17">
-        <v>11.707</v>
+        <v>9.154</v>
       </c>
       <c r="R17">
-        <v>23.354</v>
+        <v>18.149</v>
       </c>
       <c r="S17">
-        <v>2.454</v>
+        <v>2.284</v>
       </c>
       <c r="T17">
-        <v>4.881</v>
+        <v>4.104</v>
       </c>
       <c r="U17">
-        <v>4.267</v>
+        <v>3.868</v>
       </c>
       <c r="V17">
-        <v>2.458</v>
+        <v>2.3</v>
       </c>
       <c r="W17">
-        <v>0.573</v>
+        <v>0.582</v>
       </c>
       <c r="X17">
-        <v>0.442</v>
+        <v>0.216</v>
       </c>
     </row>
     <row r="18" spans="1:24">
       <c r="A18">
-        <v>823958</v>
+        <v>824850</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
       </c>
       <c r="C18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18">
+        <v>621121</v>
+      </c>
+      <c r="E18" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" t="s">
         <v>83</v>
       </c>
-      <c r="D18">
-        <v>607192</v>
-      </c>
-      <c r="E18" t="s">
-        <v>84</v>
-      </c>
-      <c r="F18" t="s">
-        <v>85</v>
-      </c>
       <c r="G18" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H18" t="s">
         <v>29</v>
       </c>
       <c r="I18" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J18" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K18">
-        <v>23.481</v>
+        <v>20.367</v>
       </c>
       <c r="L18">
-        <v>5.938</v>
+        <v>4.259</v>
       </c>
       <c r="M18">
-        <v>0.413</v>
+        <v>0.096</v>
       </c>
       <c r="N18">
-        <v>0.209</v>
+        <v>0.426</v>
       </c>
       <c r="O18">
-        <v>0.379</v>
+        <v>0.479</v>
       </c>
       <c r="P18">
-        <v>0.543</v>
+        <v>0.095</v>
       </c>
       <c r="Q18">
-        <v>22.992</v>
+        <v>6.93</v>
       </c>
       <c r="R18">
-        <v>39.561</v>
+        <v>16.275</v>
       </c>
       <c r="S18">
-        <v>1.789</v>
+        <v>3.037</v>
       </c>
       <c r="T18">
-        <v>4.101</v>
+        <v>4.721</v>
       </c>
       <c r="U18">
-        <v>7.488</v>
+        <v>3.886</v>
       </c>
       <c r="V18">
-        <v>1.681</v>
+        <v>3.164</v>
       </c>
       <c r="W18">
-        <v>0.615</v>
+        <v>0.738</v>
       </c>
       <c r="X18">
-        <v>0.984</v>
+        <v>0.268</v>
       </c>
     </row>
     <row r="19" spans="1:24">
       <c r="A19">
-        <v>823958</v>
+        <v>824850</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D19">
-        <v>645261</v>
+        <v>687064</v>
       </c>
       <c r="E19" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F19" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" t="s">
         <v>34</v>
       </c>
-      <c r="H19" t="s">
-        <v>35</v>
-      </c>
       <c r="I19" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="J19" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="K19">
-        <v>24.679</v>
+        <v>22.978</v>
       </c>
       <c r="L19">
-        <v>5.865</v>
+        <v>5.46</v>
       </c>
       <c r="M19">
-        <v>0.17</v>
+        <v>0.382</v>
       </c>
       <c r="N19">
-        <v>0.45</v>
+        <v>0.207</v>
       </c>
       <c r="O19">
-        <v>0.381</v>
+        <v>0.411</v>
       </c>
       <c r="P19">
-        <v>0.494</v>
+        <v>0.376</v>
       </c>
       <c r="Q19">
-        <v>11.774</v>
+        <v>12.069</v>
       </c>
       <c r="R19">
-        <v>24.069</v>
+        <v>23.598</v>
       </c>
       <c r="S19">
-        <v>2.736</v>
+        <v>2.481</v>
       </c>
       <c r="T19">
-        <v>5.377</v>
+        <v>5.069</v>
       </c>
       <c r="U19">
-        <v>3.896</v>
+        <v>3.621</v>
       </c>
       <c r="V19">
-        <v>2.051</v>
+        <v>1.672</v>
       </c>
       <c r="W19">
-        <v>0.808</v>
+        <v>0.828</v>
       </c>
       <c r="X19">
-        <v>0.685</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="20" spans="1:24">
       <c r="A20">
-        <v>824445</v>
+        <v>824929</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
       </c>
       <c r="C20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20">
+        <v>664285</v>
+      </c>
+      <c r="E20" t="s">
+        <v>87</v>
+      </c>
+      <c r="F20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G20" t="s">
+        <v>44</v>
+      </c>
+      <c r="H20" t="s">
+        <v>29</v>
+      </c>
+      <c r="I20" t="s">
+        <v>89</v>
+      </c>
+      <c r="J20" t="s">
         <v>90</v>
       </c>
-      <c r="D20">
-        <v>656876</v>
-      </c>
-      <c r="E20" t="s">
-        <v>91</v>
-      </c>
-      <c r="F20" t="s">
-        <v>92</v>
-      </c>
-      <c r="G20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H20" t="s">
-        <v>35</v>
-      </c>
-      <c r="I20" t="s">
-        <v>93</v>
-      </c>
-      <c r="J20" t="s">
-        <v>94</v>
-      </c>
       <c r="K20">
-        <v>21.836</v>
+        <v>23.374</v>
       </c>
       <c r="L20">
-        <v>5.58</v>
+        <v>5.311</v>
       </c>
       <c r="M20">
-        <v>0.228</v>
+        <v>0.204</v>
       </c>
       <c r="N20">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="O20">
-        <v>0.493</v>
+        <v>0.486</v>
       </c>
       <c r="P20">
-        <v>0.448</v>
+        <v>0.35</v>
       </c>
       <c r="Q20">
-        <v>15.265</v>
+        <v>9.622</v>
       </c>
       <c r="R20">
-        <v>27.272</v>
+        <v>20.91</v>
       </c>
       <c r="S20">
-        <v>1.603</v>
+        <v>2.864</v>
       </c>
       <c r="T20">
-        <v>3.813</v>
+        <v>5.436</v>
       </c>
       <c r="U20">
-        <v>4.06</v>
+        <v>3.647</v>
       </c>
       <c r="V20">
-        <v>1.423</v>
+        <v>2.438</v>
       </c>
       <c r="W20">
-        <v>0.474</v>
+        <v>0.631</v>
       </c>
       <c r="X20">
-        <v>0.476</v>
+        <v>0.613</v>
       </c>
     </row>
     <row r="21" spans="1:24">
       <c r="A21">
-        <v>824445</v>
+        <v>824929</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
       </c>
       <c r="C21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21">
+        <v>693821</v>
+      </c>
+      <c r="E21" t="s">
+        <v>91</v>
+      </c>
+      <c r="F21" t="s">
+        <v>92</v>
+      </c>
+      <c r="G21" t="s">
+        <v>28</v>
+      </c>
+      <c r="H21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I21" t="s">
         <v>90</v>
       </c>
-      <c r="D21">
-        <v>668909</v>
-      </c>
-      <c r="E21" t="s">
-        <v>95</v>
-      </c>
-      <c r="F21" t="s">
-        <v>96</v>
-      </c>
-      <c r="G21" t="s">
-        <v>34</v>
-      </c>
-      <c r="H21" t="s">
-        <v>29</v>
-      </c>
-      <c r="I21" t="s">
-        <v>94</v>
-      </c>
       <c r="J21" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="K21">
-        <v>24.554</v>
+        <v>24.114</v>
       </c>
       <c r="L21">
-        <v>6.023</v>
+        <v>5.452</v>
       </c>
       <c r="M21">
-        <v>0.294</v>
+        <v>0.283</v>
       </c>
       <c r="N21">
-        <v>0.335</v>
+        <v>0.337</v>
       </c>
       <c r="O21">
-        <v>0.371</v>
+        <v>0.381</v>
       </c>
       <c r="P21">
-        <v>0.571</v>
+        <v>0.377</v>
       </c>
       <c r="Q21">
-        <v>20.415</v>
+        <v>12.488</v>
       </c>
       <c r="R21">
-        <v>36.599</v>
+        <v>25.359</v>
       </c>
       <c r="S21">
-        <v>1.862</v>
+        <v>2.96</v>
       </c>
       <c r="T21">
-        <v>3.803</v>
+        <v>5.682</v>
       </c>
       <c r="U21">
-        <v>6.689</v>
+        <v>4.893</v>
       </c>
       <c r="V21">
-        <v>2.883</v>
+        <v>2.305</v>
       </c>
       <c r="W21">
-        <v>0.503</v>
+        <v>0.779</v>
       </c>
       <c r="X21">
-        <v>0.797</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="22" spans="1:24">
       <c r="A22">
-        <v>824525</v>
+        <v>825016</v>
       </c>
       <c r="B22" t="s">
         <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="D22">
-        <v>608372</v>
+        <v>605488</v>
       </c>
       <c r="E22" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" t="s">
+        <v>44</v>
+      </c>
+      <c r="H22" t="s">
+        <v>34</v>
+      </c>
+      <c r="I22" t="s">
+        <v>96</v>
+      </c>
+      <c r="J22" t="s">
         <v>97</v>
       </c>
-      <c r="F22" t="s">
-        <v>98</v>
-      </c>
-      <c r="G22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H22" t="s">
-        <v>35</v>
-      </c>
-      <c r="I22" t="s">
-        <v>99</v>
-      </c>
-      <c r="J22" t="s">
-        <v>100</v>
-      </c>
       <c r="K22">
-        <v>21.144</v>
+        <v>23.894</v>
       </c>
       <c r="L22">
-        <v>4.919</v>
+        <v>5.763</v>
       </c>
       <c r="M22">
-        <v>0.161</v>
+        <v>0.4</v>
       </c>
       <c r="N22">
-        <v>0.349</v>
+        <v>0.22</v>
       </c>
       <c r="O22">
-        <v>0.49</v>
+        <v>0.38</v>
       </c>
       <c r="P22">
-        <v>0.22</v>
+        <v>0.449</v>
       </c>
       <c r="Q22">
-        <v>10.203</v>
+        <v>13.593</v>
       </c>
       <c r="R22">
-        <v>20.182</v>
+        <v>26.001</v>
       </c>
       <c r="S22">
-        <v>2.733</v>
+        <v>2.521</v>
       </c>
       <c r="T22">
-        <v>4.663</v>
+        <v>4.87</v>
       </c>
       <c r="U22">
-        <v>3.927</v>
+        <v>4.026</v>
       </c>
       <c r="V22">
-        <v>1.834</v>
+        <v>1.815</v>
       </c>
       <c r="W22">
-        <v>1.094</v>
+        <v>0.873</v>
       </c>
       <c r="X22">
-        <v>0.62</v>
+        <v>0.744</v>
       </c>
     </row>
     <row r="23" spans="1:24">
       <c r="A23">
-        <v>824525</v>
+        <v>825016</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="D23">
-        <v>682227</v>
+        <v>702070</v>
       </c>
       <c r="E23" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F23" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G23" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="H23" t="s">
         <v>29</v>
       </c>
       <c r="I23" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J23" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K23">
-        <v>22.441</v>
+        <v>22.725</v>
       </c>
       <c r="L23">
-        <v>5.19</v>
+        <v>4.959</v>
       </c>
       <c r="M23">
-        <v>0.293</v>
+        <v>0.14</v>
       </c>
       <c r="N23">
-        <v>0.269</v>
+        <v>0.429</v>
       </c>
       <c r="O23">
-        <v>0.438</v>
+        <v>0.43</v>
       </c>
       <c r="P23">
-        <v>0.31</v>
+        <v>0.237</v>
       </c>
       <c r="Q23">
-        <v>11.69</v>
+        <v>8.973</v>
       </c>
       <c r="R23">
-        <v>23.164</v>
+        <v>19.733</v>
       </c>
       <c r="S23">
-        <v>2.528</v>
+        <v>3.416</v>
       </c>
       <c r="T23">
-        <v>5.044</v>
+        <v>6.042</v>
       </c>
       <c r="U23">
-        <v>4.06</v>
+        <v>4.438</v>
       </c>
       <c r="V23">
-        <v>2.003</v>
+        <v>1.944</v>
       </c>
       <c r="W23">
-        <v>0.682</v>
+        <v>1.056</v>
       </c>
       <c r="X23">
-        <v>0.488</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24">
-      <c r="A24">
-        <v>824608</v>
-      </c>
-      <c r="B24" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" t="s">
-        <v>90</v>
-      </c>
-      <c r="D24">
-        <v>579328</v>
-      </c>
-      <c r="E24" t="s">
-        <v>103</v>
-      </c>
-      <c r="F24" t="s">
-        <v>104</v>
-      </c>
-      <c r="G24" t="s">
-        <v>28</v>
-      </c>
-      <c r="H24" t="s">
-        <v>35</v>
-      </c>
-      <c r="I24" t="s">
-        <v>105</v>
-      </c>
-      <c r="J24" t="s">
-        <v>106</v>
-      </c>
-      <c r="K24">
-        <v>21.851</v>
-      </c>
-      <c r="L24">
-        <v>5.154</v>
-      </c>
-      <c r="M24">
-        <v>0.229</v>
-      </c>
-      <c r="N24">
-        <v>0.243</v>
-      </c>
-      <c r="O24">
-        <v>0.528</v>
-      </c>
-      <c r="P24">
-        <v>0.319</v>
-      </c>
-      <c r="Q24">
-        <v>14.24</v>
-      </c>
-      <c r="R24">
-        <v>26.577</v>
-      </c>
-      <c r="S24">
-        <v>2.161</v>
-      </c>
-      <c r="T24">
-        <v>4.666</v>
-      </c>
-      <c r="U24">
-        <v>4.982</v>
-      </c>
-      <c r="V24">
-        <v>1.872</v>
-      </c>
-      <c r="W24">
-        <v>0.526</v>
-      </c>
-      <c r="X24">
-        <v>0.295</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24">
-      <c r="A25">
-        <v>824608</v>
-      </c>
-      <c r="B25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25">
-        <v>607200</v>
-      </c>
-      <c r="E25" t="s">
-        <v>107</v>
-      </c>
-      <c r="F25" t="s">
-        <v>108</v>
-      </c>
-      <c r="G25" t="s">
-        <v>34</v>
-      </c>
-      <c r="H25" t="s">
-        <v>29</v>
-      </c>
-      <c r="I25" t="s">
-        <v>106</v>
-      </c>
-      <c r="J25" t="s">
-        <v>105</v>
-      </c>
-      <c r="K25">
-        <v>22.123</v>
-      </c>
-      <c r="L25">
-        <v>5.059</v>
-      </c>
-      <c r="M25">
-        <v>0.199</v>
-      </c>
-      <c r="N25">
-        <v>0.38</v>
-      </c>
-      <c r="O25">
-        <v>0.421</v>
-      </c>
-      <c r="P25">
-        <v>0.261</v>
-      </c>
-      <c r="Q25">
-        <v>8.919</v>
-      </c>
-      <c r="R25">
-        <v>19.007</v>
-      </c>
-      <c r="S25">
-        <v>2.554</v>
-      </c>
-      <c r="T25">
-        <v>4.6</v>
-      </c>
-      <c r="U25">
-        <v>3.085</v>
-      </c>
-      <c r="V25">
-        <v>2.618</v>
-      </c>
-      <c r="W25">
-        <v>0.712</v>
-      </c>
-      <c r="X25">
-        <v>0.652</v>
-      </c>
-    </row>
-    <row r="26" spans="1:24">
-      <c r="A26">
-        <v>824850</v>
-      </c>
-      <c r="B26" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" t="s">
-        <v>109</v>
-      </c>
-      <c r="D26">
-        <v>605135</v>
-      </c>
-      <c r="E26" t="s">
-        <v>110</v>
-      </c>
-      <c r="F26" t="s">
-        <v>111</v>
-      </c>
-      <c r="G26" t="s">
-        <v>34</v>
-      </c>
-      <c r="H26" t="s">
-        <v>29</v>
-      </c>
-      <c r="I26" t="s">
-        <v>112</v>
-      </c>
-      <c r="J26" t="s">
-        <v>113</v>
-      </c>
-      <c r="K26">
-        <v>19.549</v>
-      </c>
-      <c r="L26">
-        <v>4.314</v>
-      </c>
-      <c r="M26">
-        <v>0.167</v>
-      </c>
-      <c r="N26">
-        <v>0.3</v>
-      </c>
-      <c r="O26">
-        <v>0.533</v>
-      </c>
-      <c r="P26">
-        <v>0.09</v>
-      </c>
-      <c r="Q26">
-        <v>6.561</v>
-      </c>
-      <c r="R26">
-        <v>14.812</v>
-      </c>
-      <c r="S26">
-        <v>2.486</v>
-      </c>
-      <c r="T26">
-        <v>4.776</v>
-      </c>
-      <c r="U26">
-        <v>2.656</v>
-      </c>
-      <c r="V26">
-        <v>2.144</v>
-      </c>
-      <c r="W26">
-        <v>0.521</v>
-      </c>
-      <c r="X26">
-        <v>0.331</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24">
-      <c r="A27">
-        <v>824850</v>
-      </c>
-      <c r="B27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27">
-        <v>663567</v>
-      </c>
-      <c r="E27" t="s">
-        <v>114</v>
-      </c>
-      <c r="F27" t="s">
-        <v>115</v>
-      </c>
-      <c r="G27" t="s">
-        <v>34</v>
-      </c>
-      <c r="H27" t="s">
-        <v>35</v>
-      </c>
-      <c r="I27" t="s">
-        <v>113</v>
-      </c>
-      <c r="J27" t="s">
-        <v>112</v>
-      </c>
-      <c r="K27">
-        <v>18.797</v>
-      </c>
-      <c r="L27">
-        <v>4.178</v>
-      </c>
-      <c r="M27">
-        <v>0.104</v>
-      </c>
-      <c r="N27">
-        <v>0.274</v>
-      </c>
-      <c r="O27">
-        <v>0.622</v>
-      </c>
-      <c r="P27">
-        <v>0.056</v>
-      </c>
-      <c r="Q27">
-        <v>8.92</v>
-      </c>
-      <c r="R27">
-        <v>17.823</v>
-      </c>
-      <c r="S27">
-        <v>2.338</v>
-      </c>
-      <c r="T27">
-        <v>4.085</v>
-      </c>
-      <c r="U27">
-        <v>3.818</v>
-      </c>
-      <c r="V27">
-        <v>2.346</v>
-      </c>
-      <c r="W27">
-        <v>0.579</v>
-      </c>
-      <c r="X27">
-        <v>0.243</v>
-      </c>
-    </row>
-    <row r="28" spans="1:24">
-      <c r="A28">
-        <v>824930</v>
-      </c>
-      <c r="B28" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" t="s">
-        <v>116</v>
-      </c>
-      <c r="D28">
-        <v>669373</v>
-      </c>
-      <c r="E28" t="s">
-        <v>117</v>
-      </c>
-      <c r="F28" t="s">
-        <v>118</v>
-      </c>
-      <c r="G28" t="s">
-        <v>28</v>
-      </c>
-      <c r="H28" t="s">
-        <v>35</v>
-      </c>
-      <c r="I28" t="s">
-        <v>119</v>
-      </c>
-      <c r="J28" t="s">
-        <v>120</v>
-      </c>
-      <c r="K28">
-        <v>23.723</v>
-      </c>
-      <c r="L28">
-        <v>5.748</v>
-      </c>
-      <c r="M28">
-        <v>0.28</v>
-      </c>
-      <c r="N28">
-        <v>0.206</v>
-      </c>
-      <c r="O28">
-        <v>0.514</v>
-      </c>
-      <c r="P28">
-        <v>0.515</v>
-      </c>
-      <c r="Q28">
-        <v>19.037</v>
-      </c>
-      <c r="R28">
-        <v>34.361</v>
-      </c>
-      <c r="S28">
-        <v>2.213</v>
-      </c>
-      <c r="T28">
-        <v>5.2</v>
-      </c>
-      <c r="U28">
-        <v>6.671</v>
-      </c>
-      <c r="V28">
-        <v>1.38</v>
-      </c>
-      <c r="W28">
-        <v>0.632</v>
-      </c>
-      <c r="X28">
-        <v>0.328</v>
-      </c>
-    </row>
-    <row r="29" spans="1:24">
-      <c r="A29">
-        <v>824930</v>
-      </c>
-      <c r="B29" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D29">
-        <v>702275</v>
-      </c>
-      <c r="E29" t="s">
-        <v>121</v>
-      </c>
-      <c r="F29" t="s">
-        <v>122</v>
-      </c>
-      <c r="G29" t="s">
-        <v>34</v>
-      </c>
-      <c r="H29" t="s">
-        <v>29</v>
-      </c>
-      <c r="I29" t="s">
-        <v>120</v>
-      </c>
-      <c r="J29" t="s">
-        <v>119</v>
-      </c>
-      <c r="K29">
-        <v>23.593</v>
-      </c>
-      <c r="L29">
-        <v>5.275</v>
-      </c>
-      <c r="M29">
-        <v>0.187</v>
-      </c>
-      <c r="N29">
-        <v>0.45</v>
-      </c>
-      <c r="O29">
-        <v>0.364</v>
-      </c>
-      <c r="P29">
-        <v>0.337</v>
-      </c>
-      <c r="Q29">
-        <v>12.01</v>
-      </c>
-      <c r="R29">
-        <v>24.53</v>
-      </c>
-      <c r="S29">
-        <v>3.018</v>
-      </c>
-      <c r="T29">
-        <v>5.375</v>
-      </c>
-      <c r="U29">
-        <v>5.097</v>
-      </c>
-      <c r="V29">
-        <v>2.59</v>
-      </c>
-      <c r="W29">
-        <v>0.829</v>
-      </c>
-      <c r="X29">
-        <v>0.259</v>
-      </c>
-    </row>
-    <row r="30" spans="1:24">
-      <c r="A30">
-        <v>825015</v>
-      </c>
-      <c r="B30" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" t="s">
-        <v>123</v>
-      </c>
-      <c r="D30">
-        <v>608379</v>
-      </c>
-      <c r="E30" t="s">
-        <v>124</v>
-      </c>
-      <c r="F30" t="s">
-        <v>125</v>
-      </c>
-      <c r="G30" t="s">
-        <v>34</v>
-      </c>
-      <c r="H30" t="s">
-        <v>35</v>
-      </c>
-      <c r="I30" t="s">
-        <v>126</v>
-      </c>
-      <c r="J30" t="s">
-        <v>127</v>
-      </c>
-      <c r="K30">
-        <v>22.355</v>
-      </c>
-      <c r="L30">
-        <v>5.107</v>
-      </c>
-      <c r="M30">
-        <v>0.193</v>
-      </c>
-      <c r="N30">
-        <v>0.308</v>
-      </c>
-      <c r="O30">
-        <v>0.499</v>
-      </c>
-      <c r="P30">
-        <v>0.281</v>
-      </c>
-      <c r="Q30">
-        <v>9.08</v>
-      </c>
-      <c r="R30">
-        <v>19.26</v>
-      </c>
-      <c r="S30">
-        <v>3.056</v>
-      </c>
-      <c r="T30">
-        <v>5.339</v>
-      </c>
-      <c r="U30">
-        <v>3.608</v>
-      </c>
-      <c r="V30">
-        <v>1.818</v>
-      </c>
-      <c r="W30">
-        <v>1.128</v>
-      </c>
-      <c r="X30">
-        <v>0.199</v>
-      </c>
-    </row>
-    <row r="31" spans="1:24">
-      <c r="A31">
-        <v>825015</v>
-      </c>
-      <c r="B31" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31" t="s">
-        <v>123</v>
-      </c>
-      <c r="D31">
-        <v>622663</v>
-      </c>
-      <c r="E31" t="s">
-        <v>128</v>
-      </c>
-      <c r="F31" t="s">
-        <v>129</v>
-      </c>
-      <c r="G31" t="s">
-        <v>34</v>
-      </c>
-      <c r="H31" t="s">
-        <v>29</v>
-      </c>
-      <c r="I31" t="s">
-        <v>127</v>
-      </c>
-      <c r="J31" t="s">
-        <v>126</v>
-      </c>
-      <c r="K31">
-        <v>23.216</v>
-      </c>
-      <c r="L31">
-        <v>5.14</v>
-      </c>
-      <c r="M31">
-        <v>0.254</v>
-      </c>
-      <c r="N31">
-        <v>0.318</v>
-      </c>
-      <c r="O31">
-        <v>0.428</v>
-      </c>
-      <c r="P31">
-        <v>0.274</v>
-      </c>
-      <c r="Q31">
-        <v>9.666</v>
-      </c>
-      <c r="R31">
-        <v>20.87</v>
-      </c>
-      <c r="S31">
-        <v>3.084</v>
-      </c>
-      <c r="T31">
-        <v>5.387</v>
-      </c>
-      <c r="U31">
-        <v>4.026</v>
-      </c>
-      <c r="V31">
-        <v>2.627</v>
-      </c>
-      <c r="W31">
-        <v>0.787</v>
-      </c>
-      <c r="X31">
-        <v>0.662</v>
+        <v>0.264</v>
       </c>
     </row>
   </sheetData>

--- a/data/BallparkPal_Pitchers.xlsx
+++ b/data/BallparkPal_Pitchers.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="130">
   <si>
     <t>GamePk</t>
   </si>
@@ -89,232 +89,322 @@
     <t>StolenBasesAllowed</t>
   </si>
   <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>Hunter Dobbins</t>
-  </si>
-  <si>
-    <t>Dobbins</t>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>6:45</t>
+  </si>
+  <si>
+    <t>Jake Irvin</t>
+  </si>
+  <si>
+    <t>Irvin</t>
   </si>
   <si>
     <t>R</t>
   </si>
   <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>WAS</t>
+  </si>
+  <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>Jacob Misiorowski</t>
+  </si>
+  <si>
+    <t>Misiorowski</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
+    <t>7:10</t>
+  </si>
+  <si>
+    <t>Robbie Ray</t>
+  </si>
+  <si>
+    <t>Ray</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB </t>
+  </si>
+  <si>
+    <t>Shane McClanahan</t>
+  </si>
+  <si>
+    <t>McClanahan</t>
+  </si>
+  <si>
+    <t>8:15</t>
+  </si>
+  <si>
+    <t>Matthew Liberatore</t>
+  </si>
+  <si>
+    <t>Liberatore</t>
+  </si>
+  <si>
     <t>STL</t>
   </si>
   <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>Emmet Sheehan</t>
+  </si>
+  <si>
+    <t>Sheehan</t>
+  </si>
+  <si>
+    <t>9:45</t>
+  </si>
+  <si>
+    <t>Cole Ragans</t>
+  </si>
+  <si>
+    <t>Ragans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KC </t>
+  </si>
+  <si>
+    <t>SEA</t>
+  </si>
+  <si>
+    <t>Bryan Woo</t>
+  </si>
+  <si>
+    <t>Woo</t>
+  </si>
+  <si>
+    <t>9:40</t>
+  </si>
+  <si>
+    <t>German Marquez</t>
+  </si>
+  <si>
+    <t>Marquez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD </t>
+  </si>
+  <si>
+    <t>CHW</t>
+  </si>
+  <si>
+    <t>Noah Schultz</t>
+  </si>
+  <si>
+    <t>Schultz</t>
+  </si>
+  <si>
+    <t>Mitch Keller</t>
+  </si>
+  <si>
+    <t>Keller</t>
+  </si>
+  <si>
     <t>PIT</t>
   </si>
   <si>
-    <t>Paul Skenes</t>
-  </si>
-  <si>
-    <t>Skenes</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>5:35</t>
-  </si>
-  <si>
-    <t>Adrian Houser</t>
-  </si>
-  <si>
-    <t>Houser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF </t>
+    <t>CIN</t>
+  </si>
+  <si>
+    <t>Brady Singer</t>
+  </si>
+  <si>
+    <t>Singer</t>
+  </si>
+  <si>
+    <t>7:05</t>
+  </si>
+  <si>
+    <t>Cade Povich</t>
+  </si>
+  <si>
+    <t>Povich</t>
+  </si>
+  <si>
+    <t>BAL</t>
+  </si>
+  <si>
+    <t>NYY</t>
+  </si>
+  <si>
+    <t>Will Warren</t>
+  </si>
+  <si>
+    <t>Warren</t>
+  </si>
+  <si>
+    <t>8:10</t>
+  </si>
+  <si>
+    <t>Patrick Corbin</t>
+  </si>
+  <si>
+    <t>Corbin</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>Simeon Woods Rich.</t>
+  </si>
+  <si>
+    <t>Woods Rich.</t>
+  </si>
+  <si>
+    <t>Zack Wheeler</t>
+  </si>
+  <si>
+    <t>Wheeler</t>
   </si>
   <si>
     <t>PHI</t>
   </si>
   <si>
-    <t>Andrew Painter</t>
-  </si>
-  <si>
-    <t>Painter</t>
-  </si>
-  <si>
-    <t>Cristopher Sanchez</t>
-  </si>
-  <si>
-    <t>Sanchez</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>Logan Webb</t>
-  </si>
-  <si>
-    <t>Webb</t>
-  </si>
-  <si>
-    <t>1:10</t>
-  </si>
-  <si>
-    <t>Miles Mikolas</t>
-  </si>
-  <si>
-    <t>Mikolas</t>
-  </si>
-  <si>
-    <t>WAS</t>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>Eury Perez</t>
+  </si>
+  <si>
+    <t>Perez</t>
+  </si>
+  <si>
+    <t>9:38</t>
+  </si>
+  <si>
+    <t>Christian Scott</t>
+  </si>
+  <si>
+    <t>Scott</t>
   </si>
   <si>
     <t>NYM</t>
   </si>
   <si>
-    <t>Freddy Peralta</t>
-  </si>
-  <si>
-    <t>Peralta</t>
-  </si>
-  <si>
-    <t>7:40</t>
-  </si>
-  <si>
-    <t>Kevin Gausman</t>
-  </si>
-  <si>
-    <t>Gausman</t>
-  </si>
-  <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>MIN</t>
-  </si>
-  <si>
-    <t>Bailey Ober</t>
-  </si>
-  <si>
-    <t>Ober</t>
-  </si>
-  <si>
-    <t>1:40</t>
-  </si>
-  <si>
-    <t>Brandon Woodruff</t>
-  </si>
-  <si>
-    <t>Woodruff</t>
-  </si>
-  <si>
-    <t>MIL</t>
+    <t>LAA</t>
+  </si>
+  <si>
+    <t>Walbert Urena</t>
+  </si>
+  <si>
+    <t>Urena</t>
+  </si>
+  <si>
+    <t>6:40</t>
+  </si>
+  <si>
+    <t>Jack Flaherty</t>
+  </si>
+  <si>
+    <t>Flaherty</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>TEX</t>
+  </si>
+  <si>
+    <t>MacKenzie Gore</t>
+  </si>
+  <si>
+    <t>Gore</t>
+  </si>
+  <si>
+    <t>8:40</t>
+  </si>
+  <si>
+    <t>Jose Quintana</t>
+  </si>
+  <si>
+    <t>Quintana</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>Grant Holmes</t>
+  </si>
+  <si>
+    <t>Holmes</t>
+  </si>
+  <si>
+    <t>2:20</t>
+  </si>
+  <si>
+    <t>Colin Rea</t>
+  </si>
+  <si>
+    <t>Rea</t>
+  </si>
+  <si>
+    <t>CHC</t>
   </si>
   <si>
     <t>ARI</t>
   </si>
   <si>
-    <t>Michael Soroka</t>
-  </si>
-  <si>
-    <t>Soroka</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>Michael Lorenzen</t>
-  </si>
-  <si>
-    <t>Lorenzen</t>
-  </si>
-  <si>
-    <t>COL</t>
-  </si>
-  <si>
-    <t>CIN</t>
-  </si>
-  <si>
-    <t>Andrew Abbott</t>
-  </si>
-  <si>
-    <t>Abbott</t>
-  </si>
-  <si>
-    <t>Chris Bassitt</t>
-  </si>
-  <si>
-    <t>Bassitt</t>
-  </si>
-  <si>
-    <t>BAL</t>
+    <t>Zac Gallen</t>
+  </si>
+  <si>
+    <t>Gallen</t>
+  </si>
+  <si>
+    <t>Mike Burrows</t>
+  </si>
+  <si>
+    <t>Burrows</t>
   </si>
   <si>
     <t>HOU</t>
   </si>
   <si>
-    <t>Peter Lambert</t>
-  </si>
-  <si>
-    <t>Lambert</t>
-  </si>
-  <si>
-    <t>4:05</t>
-  </si>
-  <si>
-    <t>Lance McCullers Jr.</t>
-  </si>
-  <si>
-    <t>McCullers Jr.</t>
-  </si>
-  <si>
-    <t>Brandon Young</t>
-  </si>
-  <si>
-    <t>Young</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>Framber Valdez</t>
-  </si>
-  <si>
-    <t>Valdez</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>ATL</t>
-  </si>
-  <si>
-    <t>Bryce Elder</t>
-  </si>
-  <si>
-    <t>Elder</t>
-  </si>
-  <si>
-    <t>3:05</t>
-  </si>
-  <si>
-    <t>Jeffrey Springs</t>
-  </si>
-  <si>
-    <t>Springs</t>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>Jake Bennett</t>
+  </si>
+  <si>
+    <t>Bennett</t>
+  </si>
+  <si>
+    <t>J.T. Ginn</t>
+  </si>
+  <si>
+    <t>Ginn</t>
   </si>
   <si>
     <t>ATH</t>
   </si>
   <si>
-    <t xml:space="preserve">KC </t>
-  </si>
-  <si>
-    <t>Noah Cameron</t>
-  </si>
-  <si>
-    <t>Cameron</t>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t>Joey Cantillo</t>
+  </si>
+  <si>
+    <t>Cantillo</t>
   </si>
 </sst>
 </file>
@@ -654,7 +744,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:24">
@@ -733,7 +823,7 @@
     </row>
     <row r="2" spans="1:24">
       <c r="A2">
-        <v>823391</v>
+        <v>822744</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
@@ -742,7 +832,7 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>690928</v>
+        <v>663623</v>
       </c>
       <c r="E2" t="s">
         <v>26</v>
@@ -763,51 +853,51 @@
         <v>31</v>
       </c>
       <c r="K2">
-        <v>20.027</v>
+        <v>22.576</v>
       </c>
       <c r="L2">
-        <v>4.714</v>
+        <v>5.025</v>
       </c>
       <c r="M2">
-        <v>0.1</v>
+        <v>0.144</v>
       </c>
       <c r="N2">
-        <v>0.419</v>
+        <v>0.495</v>
       </c>
       <c r="O2">
-        <v>0.481</v>
+        <v>0.361</v>
       </c>
       <c r="P2">
-        <v>0.174</v>
+        <v>0.25</v>
       </c>
       <c r="Q2">
-        <v>9.675</v>
+        <v>11.768</v>
       </c>
       <c r="R2">
-        <v>18.928</v>
+        <v>23.724</v>
       </c>
       <c r="S2">
-        <v>2.104</v>
+        <v>2.928</v>
       </c>
       <c r="T2">
-        <v>4.467</v>
+        <v>5.458</v>
       </c>
       <c r="U2">
-        <v>3.266</v>
+        <v>5.19</v>
       </c>
       <c r="V2">
-        <v>1.632</v>
+        <v>2.275</v>
       </c>
       <c r="W2">
-        <v>0.486</v>
+        <v>0.834</v>
       </c>
       <c r="X2">
-        <v>0.243</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="3" spans="1:24">
       <c r="A3">
-        <v>823391</v>
+        <v>822744</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
@@ -816,7 +906,7 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>694973</v>
+        <v>694819</v>
       </c>
       <c r="E3" t="s">
         <v>32</v>
@@ -837,51 +927,51 @@
         <v>30</v>
       </c>
       <c r="K3">
-        <v>23.053</v>
+        <v>21.439</v>
       </c>
       <c r="L3">
-        <v>5.949</v>
+        <v>5.142</v>
       </c>
       <c r="M3">
-        <v>0.416</v>
+        <v>0.264</v>
       </c>
       <c r="N3">
-        <v>0.174</v>
+        <v>0.159</v>
       </c>
       <c r="O3">
-        <v>0.41</v>
+        <v>0.577</v>
       </c>
       <c r="P3">
-        <v>0.564</v>
+        <v>0.304</v>
       </c>
       <c r="Q3">
-        <v>21.761</v>
+        <v>20.261</v>
       </c>
       <c r="R3">
-        <v>37.35</v>
+        <v>35.179</v>
       </c>
       <c r="S3">
-        <v>1.387</v>
+        <v>1.715</v>
       </c>
       <c r="T3">
-        <v>3.579</v>
+        <v>3.877</v>
       </c>
       <c r="U3">
-        <v>6.304</v>
+        <v>7.365</v>
       </c>
       <c r="V3">
-        <v>1.727</v>
+        <v>2.244</v>
       </c>
       <c r="W3">
-        <v>0.458</v>
+        <v>0.501</v>
       </c>
       <c r="X3">
-        <v>0.321</v>
+        <v>0.478</v>
       </c>
     </row>
     <row r="4" spans="1:24">
       <c r="A4">
-        <v>823471</v>
+        <v>822990</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -890,7 +980,7 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>605288</v>
+        <v>592662</v>
       </c>
       <c r="E4" t="s">
         <v>36</v>
@@ -899,63 +989,63 @@
         <v>37</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K4">
-        <v>22.325</v>
+        <v>21.884</v>
       </c>
       <c r="L4">
-        <v>4.94</v>
+        <v>4.972</v>
       </c>
       <c r="M4">
-        <v>0.164</v>
+        <v>0.182</v>
       </c>
       <c r="N4">
-        <v>0.395</v>
+        <v>0.381</v>
       </c>
       <c r="O4">
-        <v>0.441</v>
+        <v>0.437</v>
       </c>
       <c r="P4">
-        <v>0.245</v>
+        <v>0.254</v>
       </c>
       <c r="Q4">
-        <v>7.859</v>
+        <v>12.265</v>
       </c>
       <c r="R4">
-        <v>18.001</v>
+        <v>23.916</v>
       </c>
       <c r="S4">
-        <v>3.039</v>
+        <v>2.509</v>
       </c>
       <c r="T4">
-        <v>5.815</v>
+        <v>4.474</v>
       </c>
       <c r="U4">
-        <v>3.446</v>
+        <v>4.807</v>
       </c>
       <c r="V4">
-        <v>2.063</v>
+        <v>2.607</v>
       </c>
       <c r="W4">
-        <v>0.644</v>
+        <v>0.647</v>
       </c>
       <c r="X4">
-        <v>0.705</v>
+        <v>0.576</v>
       </c>
     </row>
     <row r="5" spans="1:24">
       <c r="A5">
-        <v>823471</v>
+        <v>822990</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -964,383 +1054,383 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>691725</v>
+        <v>663556</v>
       </c>
       <c r="E5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" t="s">
         <v>40</v>
       </c>
-      <c r="F5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>39</v>
       </c>
-      <c r="J5" t="s">
-        <v>38</v>
-      </c>
       <c r="K5">
-        <v>22.136</v>
+        <v>22.266</v>
       </c>
       <c r="L5">
-        <v>5.026</v>
+        <v>5.317</v>
       </c>
       <c r="M5">
-        <v>0.311</v>
+        <v>0.322</v>
       </c>
       <c r="N5">
-        <v>0.25</v>
+        <v>0.272</v>
       </c>
       <c r="O5">
-        <v>0.439</v>
+        <v>0.405</v>
       </c>
       <c r="P5">
-        <v>0.27</v>
+        <v>0.352</v>
       </c>
       <c r="Q5">
-        <v>11.33</v>
+        <v>16.808</v>
       </c>
       <c r="R5">
-        <v>22.735</v>
+        <v>30.394</v>
       </c>
       <c r="S5">
-        <v>2.386</v>
+        <v>2.084</v>
       </c>
       <c r="T5">
-        <v>5.042</v>
+        <v>4.745</v>
       </c>
       <c r="U5">
-        <v>3.955</v>
+        <v>5.785</v>
       </c>
       <c r="V5">
-        <v>2.24</v>
+        <v>1.695</v>
       </c>
       <c r="W5">
-        <v>0.584</v>
+        <v>0.591</v>
       </c>
       <c r="X5">
-        <v>0.193</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="6" spans="1:24">
       <c r="A6">
-        <v>823472</v>
+        <v>823066</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D6">
-        <v>650911</v>
+        <v>669461</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I6" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J6" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K6">
-        <v>24.607</v>
+        <v>23.139</v>
       </c>
       <c r="L6">
-        <v>6.039</v>
+        <v>5.276</v>
       </c>
       <c r="M6">
-        <v>0.376</v>
+        <v>0.177</v>
       </c>
       <c r="N6">
-        <v>0.259</v>
+        <v>0.457</v>
       </c>
       <c r="O6">
         <v>0.366</v>
       </c>
       <c r="P6">
-        <v>0.565</v>
+        <v>0.311</v>
       </c>
       <c r="Q6">
-        <v>19.901</v>
+        <v>8.826</v>
       </c>
       <c r="R6">
-        <v>35.916</v>
+        <v>19.253</v>
       </c>
       <c r="S6">
-        <v>1.946</v>
+        <v>2.77</v>
       </c>
       <c r="T6">
-        <v>5.442</v>
+        <v>5.787</v>
       </c>
       <c r="U6">
-        <v>6.375</v>
+        <v>3.142</v>
       </c>
       <c r="V6">
-        <v>1.38</v>
+        <v>1.721</v>
       </c>
       <c r="W6">
-        <v>0.445</v>
+        <v>0.669</v>
       </c>
       <c r="X6">
-        <v>0.244</v>
+        <v>0.601</v>
       </c>
     </row>
     <row r="7" spans="1:24">
       <c r="A7">
-        <v>823472</v>
+        <v>823066</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D7">
-        <v>657277</v>
+        <v>686218</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G7" t="s">
         <v>28</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I7" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="J7" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="K7">
-        <v>23.799</v>
+        <v>18.834</v>
       </c>
       <c r="L7">
-        <v>5.632</v>
+        <v>4.529</v>
       </c>
       <c r="M7">
-        <v>0.197</v>
+        <v>0.154</v>
       </c>
       <c r="N7">
-        <v>0.398</v>
+        <v>0.177</v>
       </c>
       <c r="O7">
-        <v>0.405</v>
+        <v>0.669</v>
       </c>
       <c r="P7">
-        <v>0.469</v>
+        <v>0.106</v>
       </c>
       <c r="Q7">
-        <v>14.158</v>
+        <v>14.031</v>
       </c>
       <c r="R7">
-        <v>27.476</v>
+        <v>24.536</v>
       </c>
       <c r="S7">
-        <v>2.388</v>
+        <v>1.6</v>
       </c>
       <c r="T7">
-        <v>5.394</v>
+        <v>3.543</v>
       </c>
       <c r="U7">
-        <v>4.894</v>
+        <v>4.799</v>
       </c>
       <c r="V7">
-        <v>1.844</v>
+        <v>1.752</v>
       </c>
       <c r="W7">
-        <v>0.496</v>
+        <v>0.41</v>
       </c>
       <c r="X7">
-        <v>0.642</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="8" spans="1:24">
       <c r="A8">
-        <v>823634</v>
+        <v>823146</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>571945</v>
+        <v>666142</v>
       </c>
       <c r="E8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K8">
-        <v>21.174</v>
+        <v>21.358</v>
       </c>
       <c r="L8">
-        <v>5.106</v>
+        <v>5.058</v>
       </c>
       <c r="M8">
-        <v>0.161</v>
+        <v>0.141</v>
       </c>
       <c r="N8">
-        <v>0.37</v>
+        <v>0.403</v>
       </c>
       <c r="O8">
-        <v>0.469</v>
+        <v>0.457</v>
       </c>
       <c r="P8">
-        <v>0.267</v>
+        <v>0.269</v>
       </c>
       <c r="Q8">
-        <v>10.485</v>
+        <v>18.202</v>
       </c>
       <c r="R8">
-        <v>20.293</v>
+        <v>32.098</v>
       </c>
       <c r="S8">
-        <v>2.249</v>
+        <v>2.101</v>
       </c>
       <c r="T8">
-        <v>4.684</v>
+        <v>3.684</v>
       </c>
       <c r="U8">
-        <v>3.229</v>
+        <v>7.103</v>
       </c>
       <c r="V8">
-        <v>1.34</v>
+        <v>2.562</v>
       </c>
       <c r="W8">
-        <v>0.783</v>
+        <v>0.797</v>
       </c>
       <c r="X8">
-        <v>0.29</v>
+        <v>0.419</v>
       </c>
     </row>
     <row r="9" spans="1:24">
       <c r="A9">
-        <v>823634</v>
+        <v>823146</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D9">
-        <v>642547</v>
+        <v>693433</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G9" t="s">
         <v>28</v>
       </c>
       <c r="H9" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K9">
-        <v>23.263</v>
+        <v>24.176</v>
       </c>
       <c r="L9">
-        <v>5.633</v>
+        <v>6.202</v>
       </c>
       <c r="M9">
-        <v>0.347</v>
+        <v>0.414</v>
       </c>
       <c r="N9">
-        <v>0.255</v>
+        <v>0.226</v>
       </c>
       <c r="O9">
-        <v>0.398</v>
+        <v>0.36</v>
       </c>
       <c r="P9">
-        <v>0.447</v>
+        <v>0.604</v>
       </c>
       <c r="Q9">
-        <v>18.12</v>
+        <v>22.061</v>
       </c>
       <c r="R9">
-        <v>32.631</v>
+        <v>38.036</v>
       </c>
       <c r="S9">
-        <v>2.007</v>
+        <v>1.678</v>
       </c>
       <c r="T9">
-        <v>4.281</v>
+        <v>4.326</v>
       </c>
       <c r="U9">
-        <v>5.961</v>
+        <v>6.522</v>
       </c>
       <c r="V9">
-        <v>2.181</v>
+        <v>1.281</v>
       </c>
       <c r="W9">
-        <v>0.615</v>
+        <v>0.623</v>
       </c>
       <c r="X9">
-        <v>0.792</v>
+        <v>0.459</v>
       </c>
     </row>
     <row r="10" spans="1:24">
       <c r="A10">
-        <v>823714</v>
+        <v>823309</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D10">
-        <v>592332</v>
+        <v>608566</v>
       </c>
       <c r="E10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s">
         <v>28</v>
@@ -1349,516 +1439,516 @@
         <v>29</v>
       </c>
       <c r="I10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K10">
-        <v>22.526</v>
+        <v>23.321</v>
       </c>
       <c r="L10">
-        <v>5.478</v>
+        <v>5.553</v>
       </c>
       <c r="M10">
-        <v>0.229</v>
+        <v>0.323</v>
       </c>
       <c r="N10">
-        <v>0.276</v>
+        <v>0.285</v>
       </c>
       <c r="O10">
-        <v>0.495</v>
+        <v>0.392</v>
       </c>
       <c r="P10">
-        <v>0.426</v>
+        <v>0.405</v>
       </c>
       <c r="Q10">
-        <v>16.849</v>
+        <v>12.074</v>
       </c>
       <c r="R10">
-        <v>30.467</v>
+        <v>23.72</v>
       </c>
       <c r="S10">
-        <v>2.133</v>
+        <v>2.421</v>
       </c>
       <c r="T10">
-        <v>4.743</v>
+        <v>4.606</v>
       </c>
       <c r="U10">
-        <v>5.784</v>
+        <v>3.588</v>
       </c>
       <c r="V10">
-        <v>1.438</v>
+        <v>2.187</v>
       </c>
       <c r="W10">
-        <v>0.678</v>
+        <v>0.812</v>
       </c>
       <c r="X10">
-        <v>0.345</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="11" spans="1:24">
       <c r="A11">
-        <v>823714</v>
+        <v>823309</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D11">
-        <v>641927</v>
+        <v>702273</v>
       </c>
       <c r="E11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G11" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H11" t="s">
         <v>34</v>
       </c>
       <c r="I11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K11">
-        <v>23.627</v>
+        <v>21.037</v>
       </c>
       <c r="L11">
-        <v>5.64</v>
+        <v>4.891</v>
       </c>
       <c r="M11">
-        <v>0.262</v>
+        <v>0.153</v>
       </c>
       <c r="N11">
-        <v>0.354</v>
+        <v>0.337</v>
       </c>
       <c r="O11">
-        <v>0.384</v>
+        <v>0.511</v>
       </c>
       <c r="P11">
-        <v>0.424</v>
+        <v>0.21</v>
       </c>
       <c r="Q11">
-        <v>13.146</v>
+        <v>12.882</v>
       </c>
       <c r="R11">
-        <v>25.394</v>
+        <v>24.189</v>
       </c>
       <c r="S11">
-        <v>2.393</v>
+        <v>2.255</v>
       </c>
       <c r="T11">
-        <v>5.283</v>
+        <v>4.317</v>
       </c>
       <c r="U11">
-        <v>4.129</v>
+        <v>4.843</v>
       </c>
       <c r="V11">
-        <v>1.513</v>
+        <v>2.207</v>
       </c>
       <c r="W11">
-        <v>0.697</v>
+        <v>0.636</v>
       </c>
       <c r="X11">
-        <v>0.344</v>
+        <v>0.457</v>
       </c>
     </row>
     <row r="12" spans="1:24">
       <c r="A12">
-        <v>823795</v>
+        <v>823389</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="D12">
-        <v>605540</v>
+        <v>656605</v>
       </c>
       <c r="E12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G12" t="s">
         <v>28</v>
       </c>
       <c r="H12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K12">
-        <v>23.534</v>
+        <v>22.677</v>
       </c>
       <c r="L12">
-        <v>5.904</v>
+        <v>5.385</v>
       </c>
       <c r="M12">
-        <v>0.393</v>
+        <v>0.284</v>
       </c>
       <c r="N12">
-        <v>0.234</v>
+        <v>0.282</v>
       </c>
       <c r="O12">
-        <v>0.374</v>
+        <v>0.435</v>
       </c>
       <c r="P12">
-        <v>0.515</v>
+        <v>0.371</v>
       </c>
       <c r="Q12">
-        <v>17.369</v>
+        <v>14.183</v>
       </c>
       <c r="R12">
-        <v>31.125</v>
+        <v>26.728</v>
       </c>
       <c r="S12">
-        <v>2.142</v>
+        <v>2.132</v>
       </c>
       <c r="T12">
-        <v>4.653</v>
+        <v>4.4</v>
       </c>
       <c r="U12">
-        <v>5.14</v>
+        <v>4.595</v>
       </c>
       <c r="V12">
-        <v>1.189</v>
+        <v>2.275</v>
       </c>
       <c r="W12">
-        <v>0.9</v>
+        <v>0.559</v>
       </c>
       <c r="X12">
-        <v>0.457</v>
+        <v>0.629</v>
       </c>
     </row>
     <row r="13" spans="1:24">
       <c r="A13">
-        <v>823795</v>
+        <v>823389</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="D13">
-        <v>647336</v>
+        <v>663903</v>
       </c>
       <c r="E13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G13" t="s">
         <v>28</v>
       </c>
       <c r="H13" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K13">
-        <v>18.701</v>
+        <v>22.34</v>
       </c>
       <c r="L13">
-        <v>4.219</v>
+        <v>5.178</v>
       </c>
       <c r="M13">
-        <v>0.087</v>
+        <v>0.181</v>
       </c>
       <c r="N13">
-        <v>0.357</v>
+        <v>0.325</v>
       </c>
       <c r="O13">
-        <v>0.556</v>
+        <v>0.494</v>
       </c>
       <c r="P13">
-        <v>0.063</v>
+        <v>0.311</v>
       </c>
       <c r="Q13">
-        <v>11.73</v>
+        <v>10.979</v>
       </c>
       <c r="R13">
-        <v>21.891</v>
+        <v>22.075</v>
       </c>
       <c r="S13">
-        <v>2.177</v>
+        <v>2.425</v>
       </c>
       <c r="T13">
-        <v>3.818</v>
+        <v>5.012</v>
       </c>
       <c r="U13">
-        <v>4.996</v>
+        <v>3.828</v>
       </c>
       <c r="V13">
-        <v>2.432</v>
+        <v>2.005</v>
       </c>
       <c r="W13">
-        <v>0.628</v>
+        <v>0.548</v>
       </c>
       <c r="X13">
-        <v>0.819</v>
+        <v>0.369</v>
       </c>
     </row>
     <row r="14" spans="1:24">
       <c r="A14">
-        <v>824524</v>
+        <v>823557</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D14">
-        <v>547179</v>
+        <v>700249</v>
       </c>
       <c r="E14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G14" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H14" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K14">
-        <v>21.223</v>
+        <v>20.486</v>
       </c>
       <c r="L14">
-        <v>4.879</v>
+        <v>4.635</v>
       </c>
       <c r="M14">
-        <v>0.174</v>
+        <v>0.135</v>
       </c>
       <c r="N14">
-        <v>0.291</v>
+        <v>0.346</v>
       </c>
       <c r="O14">
-        <v>0.535</v>
+        <v>0.519</v>
       </c>
       <c r="P14">
-        <v>0.222</v>
+        <v>0.139</v>
       </c>
       <c r="Q14">
-        <v>10.446</v>
+        <v>9.651</v>
       </c>
       <c r="R14">
-        <v>20.828</v>
+        <v>19.348</v>
       </c>
       <c r="S14">
-        <v>2.466</v>
+        <v>2.519</v>
       </c>
       <c r="T14">
-        <v>4.85</v>
+        <v>4.487</v>
       </c>
       <c r="U14">
-        <v>3.886</v>
+        <v>3.879</v>
       </c>
       <c r="V14">
-        <v>1.935</v>
+        <v>2.244</v>
       </c>
       <c r="W14">
-        <v>0.685</v>
+        <v>0.772</v>
       </c>
       <c r="X14">
-        <v>0.555</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="15" spans="1:24">
       <c r="A15">
-        <v>824524</v>
+        <v>823557</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D15">
-        <v>671096</v>
+        <v>701542</v>
       </c>
       <c r="E15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" t="s">
+        <v>74</v>
+      </c>
+      <c r="J15" t="s">
         <v>73</v>
       </c>
-      <c r="F15" t="s">
-        <v>74</v>
-      </c>
-      <c r="G15" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" t="s">
-        <v>34</v>
-      </c>
-      <c r="I15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J15" t="s">
-        <v>71</v>
-      </c>
       <c r="K15">
-        <v>23.608</v>
+        <v>23.869</v>
       </c>
       <c r="L15">
-        <v>5.463</v>
+        <v>5.695</v>
       </c>
       <c r="M15">
-        <v>0.279</v>
+        <v>0.347</v>
       </c>
       <c r="N15">
-        <v>0.32</v>
+        <v>0.282</v>
       </c>
       <c r="O15">
-        <v>0.4</v>
+        <v>0.371</v>
       </c>
       <c r="P15">
-        <v>0.365</v>
+        <v>0.431</v>
       </c>
       <c r="Q15">
-        <v>13.072</v>
+        <v>17.159</v>
       </c>
       <c r="R15">
-        <v>25.642</v>
+        <v>31.529</v>
       </c>
       <c r="S15">
-        <v>2.819</v>
+        <v>2.449</v>
       </c>
       <c r="T15">
-        <v>5.906</v>
+        <v>4.994</v>
       </c>
       <c r="U15">
-        <v>4.857</v>
+        <v>5.995</v>
       </c>
       <c r="V15">
-        <v>1.471</v>
+        <v>1.94</v>
       </c>
       <c r="W15">
-        <v>0.838</v>
+        <v>0.907</v>
       </c>
       <c r="X15">
-        <v>0.606</v>
+        <v>0.296</v>
       </c>
     </row>
     <row r="16" spans="1:24">
       <c r="A16">
-        <v>824848</v>
+        <v>823713</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="D16">
-        <v>605135</v>
+        <v>571578</v>
       </c>
       <c r="E16" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H16" t="s">
         <v>34</v>
       </c>
       <c r="I16" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J16" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K16">
-        <v>19.666</v>
+        <v>20.676</v>
       </c>
       <c r="L16">
-        <v>4.339</v>
+        <v>4.53</v>
       </c>
       <c r="M16">
-        <v>0.176</v>
+        <v>0.127</v>
       </c>
       <c r="N16">
-        <v>0.306</v>
+        <v>0.357</v>
       </c>
       <c r="O16">
-        <v>0.519</v>
+        <v>0.517</v>
       </c>
       <c r="P16">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="Q16">
-        <v>6.741</v>
+        <v>8.488</v>
       </c>
       <c r="R16">
-        <v>15.122</v>
+        <v>18.216</v>
       </c>
       <c r="S16">
-        <v>2.456</v>
+        <v>2.616</v>
       </c>
       <c r="T16">
-        <v>4.797</v>
+        <v>5.182</v>
       </c>
       <c r="U16">
-        <v>2.687</v>
+        <v>3.717</v>
       </c>
       <c r="V16">
-        <v>2.18</v>
+        <v>2.181</v>
       </c>
       <c r="W16">
-        <v>0.478</v>
+        <v>0.495</v>
       </c>
       <c r="X16">
-        <v>0.36</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="17" spans="1:24">
       <c r="A17">
-        <v>824848</v>
+        <v>823713</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="D17">
-        <v>663567</v>
+        <v>680573</v>
       </c>
       <c r="E17" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F17" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G17" t="s">
         <v>28</v>
@@ -1867,496 +1957,1088 @@
         <v>29</v>
       </c>
       <c r="I17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J17" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K17">
-        <v>18.835</v>
+        <v>22.886</v>
       </c>
       <c r="L17">
-        <v>4.2</v>
+        <v>5.375</v>
       </c>
       <c r="M17">
-        <v>0.095</v>
+        <v>0.319</v>
       </c>
       <c r="N17">
-        <v>0.285</v>
+        <v>0.275</v>
       </c>
       <c r="O17">
-        <v>0.62</v>
+        <v>0.406</v>
       </c>
       <c r="P17">
-        <v>0.057</v>
+        <v>0.35</v>
       </c>
       <c r="Q17">
-        <v>9.154</v>
+        <v>11.988</v>
       </c>
       <c r="R17">
-        <v>18.149</v>
+        <v>23.551</v>
       </c>
       <c r="S17">
-        <v>2.284</v>
+        <v>2.344</v>
       </c>
       <c r="T17">
-        <v>4.104</v>
+        <v>4.981</v>
       </c>
       <c r="U17">
-        <v>3.868</v>
+        <v>3.715</v>
       </c>
       <c r="V17">
-        <v>2.3</v>
+        <v>1.906</v>
       </c>
       <c r="W17">
-        <v>0.582</v>
+        <v>0.633</v>
       </c>
       <c r="X17">
-        <v>0.216</v>
+        <v>0.388</v>
       </c>
     </row>
     <row r="18" spans="1:24">
       <c r="A18">
-        <v>824850</v>
+        <v>823877</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="D18">
-        <v>621121</v>
+        <v>554430</v>
       </c>
       <c r="E18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G18" t="s">
         <v>28</v>
       </c>
       <c r="H18" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I18" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J18" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K18">
-        <v>20.367</v>
+        <v>23.776</v>
       </c>
       <c r="L18">
-        <v>4.259</v>
+        <v>5.916</v>
       </c>
       <c r="M18">
-        <v>0.096</v>
+        <v>0.308</v>
       </c>
       <c r="N18">
-        <v>0.426</v>
+        <v>0.207</v>
       </c>
       <c r="O18">
-        <v>0.479</v>
+        <v>0.485</v>
       </c>
       <c r="P18">
-        <v>0.095</v>
+        <v>0.605</v>
       </c>
       <c r="Q18">
-        <v>6.93</v>
+        <v>21.12</v>
       </c>
       <c r="R18">
-        <v>16.275</v>
+        <v>37.342</v>
       </c>
       <c r="S18">
-        <v>3.037</v>
+        <v>1.795</v>
       </c>
       <c r="T18">
-        <v>4.721</v>
+        <v>4.027</v>
       </c>
       <c r="U18">
-        <v>3.886</v>
+        <v>6.904</v>
       </c>
       <c r="V18">
-        <v>3.164</v>
+        <v>2.094</v>
       </c>
       <c r="W18">
-        <v>0.738</v>
+        <v>0.525</v>
       </c>
       <c r="X18">
-        <v>0.268</v>
+        <v>0.463</v>
       </c>
     </row>
     <row r="19" spans="1:24">
       <c r="A19">
-        <v>824850</v>
+        <v>823877</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="D19">
-        <v>687064</v>
+        <v>691587</v>
       </c>
       <c r="E19" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F19" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G19" t="s">
         <v>28</v>
       </c>
       <c r="H19" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I19" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J19" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="K19">
-        <v>22.978</v>
+        <v>22.594</v>
       </c>
       <c r="L19">
-        <v>5.46</v>
+        <v>5.256</v>
       </c>
       <c r="M19">
-        <v>0.382</v>
+        <v>0.17</v>
       </c>
       <c r="N19">
-        <v>0.207</v>
+        <v>0.446</v>
       </c>
       <c r="O19">
-        <v>0.411</v>
+        <v>0.385</v>
       </c>
       <c r="P19">
-        <v>0.376</v>
+        <v>0.33</v>
       </c>
       <c r="Q19">
-        <v>12.069</v>
+        <v>15.171</v>
       </c>
       <c r="R19">
-        <v>23.598</v>
+        <v>28.32</v>
       </c>
       <c r="S19">
-        <v>2.481</v>
+        <v>2.38</v>
       </c>
       <c r="T19">
-        <v>5.069</v>
+        <v>4.574</v>
       </c>
       <c r="U19">
-        <v>3.621</v>
+        <v>5.785</v>
       </c>
       <c r="V19">
-        <v>1.672</v>
+        <v>2.344</v>
       </c>
       <c r="W19">
-        <v>0.828</v>
+        <v>0.677</v>
       </c>
       <c r="X19">
-        <v>0.24</v>
+        <v>0.738</v>
       </c>
     </row>
     <row r="20" spans="1:24">
       <c r="A20">
-        <v>824929</v>
+        <v>824041</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D20">
-        <v>664285</v>
+        <v>681035</v>
       </c>
       <c r="E20" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G20" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H20" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I20" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J20" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K20">
-        <v>23.374</v>
+        <v>20.712</v>
       </c>
       <c r="L20">
-        <v>5.311</v>
+        <v>4.542</v>
       </c>
       <c r="M20">
-        <v>0.204</v>
+        <v>0.134</v>
       </c>
       <c r="N20">
-        <v>0.31</v>
+        <v>0.295</v>
       </c>
       <c r="O20">
-        <v>0.486</v>
+        <v>0.571</v>
       </c>
       <c r="P20">
-        <v>0.35</v>
+        <v>0.165</v>
       </c>
       <c r="Q20">
-        <v>9.622</v>
+        <v>11.084</v>
       </c>
       <c r="R20">
-        <v>20.91</v>
+        <v>22.092</v>
       </c>
       <c r="S20">
-        <v>2.864</v>
+        <v>2.542</v>
       </c>
       <c r="T20">
-        <v>5.436</v>
+        <v>3.989</v>
       </c>
       <c r="U20">
-        <v>3.647</v>
+        <v>4.876</v>
       </c>
       <c r="V20">
-        <v>2.438</v>
+        <v>3.246</v>
       </c>
       <c r="W20">
-        <v>0.631</v>
+        <v>0.693</v>
       </c>
       <c r="X20">
-        <v>0.613</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="21" spans="1:24">
       <c r="A21">
-        <v>824929</v>
+        <v>824041</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D21">
-        <v>693821</v>
+        <v>700712</v>
       </c>
       <c r="E21" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F21" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G21" t="s">
         <v>28</v>
       </c>
       <c r="H21" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I21" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="J21" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="K21">
-        <v>24.114</v>
+        <v>19.258</v>
       </c>
       <c r="L21">
-        <v>5.452</v>
+        <v>4.293</v>
       </c>
       <c r="M21">
-        <v>0.283</v>
+        <v>0.15</v>
       </c>
       <c r="N21">
-        <v>0.337</v>
+        <v>0.277</v>
       </c>
       <c r="O21">
-        <v>0.381</v>
+        <v>0.573</v>
       </c>
       <c r="P21">
-        <v>0.377</v>
+        <v>0.082</v>
       </c>
       <c r="Q21">
-        <v>12.488</v>
+        <v>10.313</v>
       </c>
       <c r="R21">
-        <v>25.359</v>
+        <v>20.268</v>
       </c>
       <c r="S21">
-        <v>2.96</v>
+        <v>2.219</v>
       </c>
       <c r="T21">
-        <v>5.682</v>
+        <v>3.928</v>
       </c>
       <c r="U21">
-        <v>4.893</v>
+        <v>4.273</v>
       </c>
       <c r="V21">
-        <v>2.305</v>
+        <v>2.827</v>
       </c>
       <c r="W21">
-        <v>0.779</v>
+        <v>0.528</v>
       </c>
       <c r="X21">
-        <v>0.311</v>
+        <v>0.464</v>
       </c>
     </row>
     <row r="22" spans="1:24">
       <c r="A22">
-        <v>825016</v>
+        <v>824287</v>
       </c>
       <c r="B22" t="s">
         <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D22">
-        <v>605488</v>
+        <v>656427</v>
       </c>
       <c r="E22" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F22" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G22" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H22" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I22" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="J22" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K22">
-        <v>23.894</v>
+        <v>20.951</v>
       </c>
       <c r="L22">
-        <v>5.763</v>
+        <v>4.515</v>
       </c>
       <c r="M22">
-        <v>0.4</v>
+        <v>0.191</v>
       </c>
       <c r="N22">
-        <v>0.22</v>
+        <v>0.309</v>
       </c>
       <c r="O22">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="P22">
-        <v>0.449</v>
+        <v>0.164</v>
       </c>
       <c r="Q22">
-        <v>13.593</v>
+        <v>11.173</v>
       </c>
       <c r="R22">
-        <v>26.001</v>
+        <v>22.525</v>
       </c>
       <c r="S22">
-        <v>2.521</v>
+        <v>2.53</v>
       </c>
       <c r="T22">
-        <v>4.87</v>
+        <v>4.264</v>
       </c>
       <c r="U22">
-        <v>4.026</v>
+        <v>4.923</v>
       </c>
       <c r="V22">
-        <v>1.815</v>
+        <v>3.296</v>
       </c>
       <c r="W22">
-        <v>0.873</v>
+        <v>0.502</v>
       </c>
       <c r="X22">
-        <v>0.744</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="23" spans="1:24">
       <c r="A23">
-        <v>825016</v>
+        <v>824287</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D23">
-        <v>702070</v>
+        <v>669022</v>
       </c>
       <c r="E23" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F23" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G23" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H23" t="s">
+        <v>34</v>
+      </c>
+      <c r="I23" t="s">
+        <v>101</v>
+      </c>
+      <c r="J23" t="s">
+        <v>100</v>
+      </c>
+      <c r="K23">
+        <v>21.017</v>
+      </c>
+      <c r="L23">
+        <v>4.546</v>
+      </c>
+      <c r="M23">
+        <v>0.164</v>
+      </c>
+      <c r="N23">
+        <v>0.293</v>
+      </c>
+      <c r="O23">
+        <v>0.543</v>
+      </c>
+      <c r="P23">
+        <v>0.165</v>
+      </c>
+      <c r="Q23">
+        <v>10.955</v>
+      </c>
+      <c r="R23">
+        <v>22.166</v>
+      </c>
+      <c r="S23">
+        <v>2.596</v>
+      </c>
+      <c r="T23">
+        <v>4.481</v>
+      </c>
+      <c r="U23">
+        <v>4.89</v>
+      </c>
+      <c r="V23">
+        <v>3.051</v>
+      </c>
+      <c r="W23">
+        <v>0.543</v>
+      </c>
+      <c r="X23">
+        <v>0.241</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24">
+      <c r="A24">
+        <v>824366</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24">
+        <v>500779</v>
+      </c>
+      <c r="E24" t="s">
+        <v>105</v>
+      </c>
+      <c r="F24" t="s">
+        <v>106</v>
+      </c>
+      <c r="G24" t="s">
+        <v>38</v>
+      </c>
+      <c r="H24" t="s">
         <v>29</v>
       </c>
-      <c r="I23" t="s">
-        <v>97</v>
-      </c>
-      <c r="J23" t="s">
-        <v>96</v>
-      </c>
-      <c r="K23">
-        <v>22.725</v>
-      </c>
-      <c r="L23">
-        <v>4.959</v>
-      </c>
-      <c r="M23">
-        <v>0.14</v>
-      </c>
-      <c r="N23">
-        <v>0.429</v>
-      </c>
-      <c r="O23">
-        <v>0.43</v>
-      </c>
-      <c r="P23">
-        <v>0.237</v>
-      </c>
-      <c r="Q23">
-        <v>8.973</v>
-      </c>
-      <c r="R23">
-        <v>19.733</v>
-      </c>
-      <c r="S23">
-        <v>3.416</v>
-      </c>
-      <c r="T23">
-        <v>6.042</v>
-      </c>
-      <c r="U23">
+      <c r="I24" t="s">
+        <v>107</v>
+      </c>
+      <c r="J24" t="s">
+        <v>108</v>
+      </c>
+      <c r="K24">
+        <v>20.916</v>
+      </c>
+      <c r="L24">
         <v>4.438</v>
       </c>
-      <c r="V23">
-        <v>1.944</v>
-      </c>
-      <c r="W23">
-        <v>1.056</v>
-      </c>
-      <c r="X23">
-        <v>0.264</v>
+      <c r="M24">
+        <v>0.155</v>
+      </c>
+      <c r="N24">
+        <v>0.397</v>
+      </c>
+      <c r="O24">
+        <v>0.448</v>
+      </c>
+      <c r="P24">
+        <v>0.132</v>
+      </c>
+      <c r="Q24">
+        <v>3.322</v>
+      </c>
+      <c r="R24">
+        <v>10.928</v>
+      </c>
+      <c r="S24">
+        <v>3.373</v>
+      </c>
+      <c r="T24">
+        <v>5.735</v>
+      </c>
+      <c r="U24">
+        <v>2.092</v>
+      </c>
+      <c r="V24">
+        <v>2.135</v>
+      </c>
+      <c r="W24">
+        <v>0.873</v>
+      </c>
+      <c r="X24">
+        <v>0.546</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24">
+      <c r="A25">
+        <v>824366</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25">
+        <v>656550</v>
+      </c>
+      <c r="E25" t="s">
+        <v>109</v>
+      </c>
+      <c r="F25" t="s">
+        <v>110</v>
+      </c>
+      <c r="G25" t="s">
+        <v>28</v>
+      </c>
+      <c r="H25" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" t="s">
+        <v>108</v>
+      </c>
+      <c r="J25" t="s">
+        <v>107</v>
+      </c>
+      <c r="K25">
+        <v>21.849</v>
+      </c>
+      <c r="L25">
+        <v>4.86</v>
+      </c>
+      <c r="M25">
+        <v>0.206</v>
+      </c>
+      <c r="N25">
+        <v>0.225</v>
+      </c>
+      <c r="O25">
+        <v>0.569</v>
+      </c>
+      <c r="P25">
+        <v>0.229</v>
+      </c>
+      <c r="Q25">
+        <v>7.926</v>
+      </c>
+      <c r="R25">
+        <v>17.797</v>
+      </c>
+      <c r="S25">
+        <v>2.98</v>
+      </c>
+      <c r="T25">
+        <v>5.443</v>
+      </c>
+      <c r="U25">
+        <v>3.335</v>
+      </c>
+      <c r="V25">
+        <v>2.129</v>
+      </c>
+      <c r="W25">
+        <v>0.73</v>
+      </c>
+      <c r="X25">
+        <v>0.246</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24">
+      <c r="A26">
+        <v>824686</v>
+      </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26">
+        <v>607067</v>
+      </c>
+      <c r="E26" t="s">
+        <v>112</v>
+      </c>
+      <c r="F26" t="s">
+        <v>113</v>
+      </c>
+      <c r="G26" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" t="s">
+        <v>114</v>
+      </c>
+      <c r="J26" t="s">
+        <v>115</v>
+      </c>
+      <c r="K26">
+        <v>22.845</v>
+      </c>
+      <c r="L26">
+        <v>5.544</v>
+      </c>
+      <c r="M26">
+        <v>0.296</v>
+      </c>
+      <c r="N26">
+        <v>0.278</v>
+      </c>
+      <c r="O26">
+        <v>0.426</v>
+      </c>
+      <c r="P26">
+        <v>0.422</v>
+      </c>
+      <c r="Q26">
+        <v>14.55</v>
+      </c>
+      <c r="R26">
+        <v>27.191</v>
+      </c>
+      <c r="S26">
+        <v>1.885</v>
+      </c>
+      <c r="T26">
+        <v>4.911</v>
+      </c>
+      <c r="U26">
+        <v>4.249</v>
+      </c>
+      <c r="V26">
+        <v>1.553</v>
+      </c>
+      <c r="W26">
+        <v>0.332</v>
+      </c>
+      <c r="X26">
+        <v>0.592</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24">
+      <c r="A27">
+        <v>824686</v>
+      </c>
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27">
+        <v>668678</v>
+      </c>
+      <c r="E27" t="s">
+        <v>116</v>
+      </c>
+      <c r="F27" t="s">
+        <v>117</v>
+      </c>
+      <c r="G27" t="s">
+        <v>28</v>
+      </c>
+      <c r="H27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I27" t="s">
+        <v>115</v>
+      </c>
+      <c r="J27" t="s">
+        <v>114</v>
+      </c>
+      <c r="K27">
+        <v>22.681</v>
+      </c>
+      <c r="L27">
+        <v>5.364</v>
+      </c>
+      <c r="M27">
+        <v>0.184</v>
+      </c>
+      <c r="N27">
+        <v>0.338</v>
+      </c>
+      <c r="O27">
+        <v>0.477</v>
+      </c>
+      <c r="P27">
+        <v>0.38</v>
+      </c>
+      <c r="Q27">
+        <v>12.54</v>
+      </c>
+      <c r="R27">
+        <v>24.453</v>
+      </c>
+      <c r="S27">
+        <v>2.165</v>
+      </c>
+      <c r="T27">
+        <v>4.763</v>
+      </c>
+      <c r="U27">
+        <v>4.077</v>
+      </c>
+      <c r="V27">
+        <v>2.075</v>
+      </c>
+      <c r="W27">
+        <v>0.475</v>
+      </c>
+      <c r="X27">
+        <v>0.399</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24">
+      <c r="A28">
+        <v>824772</v>
+      </c>
+      <c r="B28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28">
+        <v>681347</v>
+      </c>
+      <c r="E28" t="s">
+        <v>118</v>
+      </c>
+      <c r="F28" t="s">
+        <v>119</v>
+      </c>
+      <c r="G28" t="s">
+        <v>28</v>
+      </c>
+      <c r="H28" t="s">
+        <v>34</v>
+      </c>
+      <c r="I28" t="s">
+        <v>120</v>
+      </c>
+      <c r="J28" t="s">
+        <v>121</v>
+      </c>
+      <c r="K28">
+        <v>22.347</v>
+      </c>
+      <c r="L28">
+        <v>5.109</v>
+      </c>
+      <c r="M28">
+        <v>0.191</v>
+      </c>
+      <c r="N28">
+        <v>0.284</v>
+      </c>
+      <c r="O28">
+        <v>0.525</v>
+      </c>
+      <c r="P28">
+        <v>0.263</v>
+      </c>
+      <c r="Q28">
+        <v>11.3</v>
+      </c>
+      <c r="R28">
+        <v>22.65</v>
+      </c>
+      <c r="S28">
+        <v>2.67</v>
+      </c>
+      <c r="T28">
+        <v>5.434</v>
+      </c>
+      <c r="U28">
+        <v>4.379</v>
+      </c>
+      <c r="V28">
+        <v>1.86</v>
+      </c>
+      <c r="W28">
+        <v>0.618</v>
+      </c>
+      <c r="X28">
+        <v>0.521</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24">
+      <c r="A29">
+        <v>824772</v>
+      </c>
+      <c r="B29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29">
+        <v>687562</v>
+      </c>
+      <c r="E29" t="s">
+        <v>122</v>
+      </c>
+      <c r="F29" t="s">
+        <v>123</v>
+      </c>
+      <c r="G29" t="s">
+        <v>38</v>
+      </c>
+      <c r="H29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I29" t="s">
+        <v>121</v>
+      </c>
+      <c r="J29" t="s">
+        <v>120</v>
+      </c>
+      <c r="K29">
+        <v>19.424</v>
+      </c>
+      <c r="L29">
+        <v>4.299</v>
+      </c>
+      <c r="M29">
+        <v>0.144</v>
+      </c>
+      <c r="N29">
+        <v>0.32</v>
+      </c>
+      <c r="O29">
+        <v>0.536</v>
+      </c>
+      <c r="P29">
+        <v>0.079</v>
+      </c>
+      <c r="Q29">
+        <v>8.558</v>
+      </c>
+      <c r="R29">
+        <v>17.64</v>
+      </c>
+      <c r="S29">
+        <v>2.456</v>
+      </c>
+      <c r="T29">
+        <v>4.637</v>
+      </c>
+      <c r="U29">
+        <v>3.644</v>
+      </c>
+      <c r="V29">
+        <v>2.141</v>
+      </c>
+      <c r="W29">
+        <v>0.567</v>
+      </c>
+      <c r="X29">
+        <v>0.222</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24">
+      <c r="A30">
+        <v>825012</v>
+      </c>
+      <c r="B30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30">
+        <v>669372</v>
+      </c>
+      <c r="E30" t="s">
+        <v>124</v>
+      </c>
+      <c r="F30" t="s">
+        <v>125</v>
+      </c>
+      <c r="G30" t="s">
+        <v>28</v>
+      </c>
+      <c r="H30" t="s">
+        <v>29</v>
+      </c>
+      <c r="I30" t="s">
+        <v>126</v>
+      </c>
+      <c r="J30" t="s">
+        <v>127</v>
+      </c>
+      <c r="K30">
+        <v>22.316</v>
+      </c>
+      <c r="L30">
+        <v>5.371</v>
+      </c>
+      <c r="M30">
+        <v>0.311</v>
+      </c>
+      <c r="N30">
+        <v>0.261</v>
+      </c>
+      <c r="O30">
+        <v>0.427</v>
+      </c>
+      <c r="P30">
+        <v>0.376</v>
+      </c>
+      <c r="Q30">
+        <v>13.2</v>
+      </c>
+      <c r="R30">
+        <v>25.081</v>
+      </c>
+      <c r="S30">
+        <v>2.047</v>
+      </c>
+      <c r="T30">
+        <v>4.383</v>
+      </c>
+      <c r="U30">
+        <v>3.912</v>
+      </c>
+      <c r="V30">
+        <v>2.085</v>
+      </c>
+      <c r="W30">
+        <v>0.53</v>
+      </c>
+      <c r="X30">
+        <v>0.495</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24">
+      <c r="A31">
+        <v>825012</v>
+      </c>
+      <c r="B31" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31">
+        <v>676282</v>
+      </c>
+      <c r="E31" t="s">
+        <v>128</v>
+      </c>
+      <c r="F31" t="s">
+        <v>129</v>
+      </c>
+      <c r="G31" t="s">
+        <v>38</v>
+      </c>
+      <c r="H31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I31" t="s">
+        <v>127</v>
+      </c>
+      <c r="J31" t="s">
+        <v>126</v>
+      </c>
+      <c r="K31">
+        <v>21.101</v>
+      </c>
+      <c r="L31">
+        <v>4.854</v>
+      </c>
+      <c r="M31">
+        <v>0.16</v>
+      </c>
+      <c r="N31">
+        <v>0.35</v>
+      </c>
+      <c r="O31">
+        <v>0.49</v>
+      </c>
+      <c r="P31">
+        <v>0.229</v>
+      </c>
+      <c r="Q31">
+        <v>13.793</v>
+      </c>
+      <c r="R31">
+        <v>25.746</v>
+      </c>
+      <c r="S31">
+        <v>2.485</v>
+      </c>
+      <c r="T31">
+        <v>4.522</v>
+      </c>
+      <c r="U31">
+        <v>5.588</v>
+      </c>
+      <c r="V31">
+        <v>2.105</v>
+      </c>
+      <c r="W31">
+        <v>0.826</v>
+      </c>
+      <c r="X31">
+        <v>0.315</v>
       </c>
     </row>
   </sheetData>
